--- a/currentbuild/StructureDefinition-parek-service-request.xlsx
+++ b/currentbuild/StructureDefinition-parek-service-request.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$79</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$83</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2951" uniqueCount="563">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3096" uniqueCount="574">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-17T13:48:48+00:00</t>
+    <t>2026-03-19T07:57:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1092,6 +1092,40 @@
     <t>Indicates the context of the order details by reference.</t>
   </si>
   <si>
+    <t>ServiceRequest.orderDetail.parameterFocus.id</t>
+  </si>
+  <si>
+    <t>ServiceRequest.orderDetail.parameterFocus.extension</t>
+  </si>
+  <si>
+    <t>ServiceRequest.orderDetail.parameterFocus.concept</t>
+  </si>
+  <si>
+    <t>Reference to a concept (by class)</t>
+  </si>
+  <si>
+    <t>A reference to a concept - e.g. the information is identified by its general class to the degree of precision found in the terminology.</t>
+  </si>
+  <si>
+    <t>CodeableReference.concept</t>
+  </si>
+  <si>
+    <t>ServiceRequest.orderDetail.parameterFocus.reference</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference
+</t>
+  </si>
+  <si>
+    <t>Reference to a resource (by instance)</t>
+  </si>
+  <si>
+    <t>A reference to a resource the provides exact details about the information being referenced.</t>
+  </si>
+  <si>
+    <t>CodeableReference.reference</t>
+  </si>
+  <si>
     <t>ServiceRequest.orderDetail.parameter</t>
   </si>
   <si>
@@ -1129,7 +1163,7 @@
   </si>
   <si>
     <t>Quantity
-CodeableConcept</t>
+CodeableConceptstring</t>
   </si>
   <si>
     <t>The value for the order detail</t>
@@ -2095,7 +2129,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO79"/>
+  <dimension ref="A1:AO83"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="46.05078125" customWidth="true" bestFit="true"/>
@@ -6143,7 +6177,7 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="G35" t="s" s="2">
         <v>90</v>
@@ -6258,10 +6292,10 @@
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>80</v>
@@ -6270,16 +6304,16 @@
         <v>80</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>329</v>
+        <v>92</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>346</v>
+        <v>161</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>347</v>
+        <v>162</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -6330,19 +6364,19 @@
         <v>80</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>345</v>
+        <v>163</v>
       </c>
       <c r="AG36" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>80</v>
+        <v>164</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>102</v>
+        <v>80</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>80</v>
@@ -6354,7 +6388,7 @@
         <v>80</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>80</v>
+        <v>165</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>80</v>
@@ -6362,21 +6396,21 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>80</v>
+        <v>137</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>80</v>
@@ -6388,15 +6422,17 @@
         <v>80</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>202</v>
+        <v>138</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>161</v>
+        <v>139</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="N37" s="2"/>
+        <v>167</v>
+      </c>
+      <c r="N37" t="s" s="2">
+        <v>141</v>
+      </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>80</v>
@@ -6433,31 +6469,31 @@
         <v>80</v>
       </c>
       <c r="AB37" t="s" s="2">
-        <v>80</v>
+        <v>168</v>
       </c>
       <c r="AC37" t="s" s="2">
-        <v>80</v>
+        <v>169</v>
       </c>
       <c r="AD37" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE37" t="s" s="2">
-        <v>80</v>
+        <v>170</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>164</v>
+        <v>80</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>80</v>
+        <v>143</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>80</v>
@@ -6477,21 +6513,21 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>137</v>
+        <v>80</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>80</v>
@@ -6500,20 +6536,18 @@
         <v>80</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>138</v>
+        <v>182</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>139</v>
+        <v>348</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>141</v>
-      </c>
+        <v>349</v>
+      </c>
+      <c r="N38" s="2"/>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>80</v>
@@ -6562,19 +6596,19 @@
         <v>80</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>171</v>
+        <v>350</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>143</v>
+        <v>102</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>80</v>
@@ -6586,7 +6620,7 @@
         <v>80</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>165</v>
+        <v>144</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>80</v>
@@ -6594,46 +6628,42 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>337</v>
+        <v>80</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I39" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="J39" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>138</v>
+        <v>352</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>338</v>
+        <v>353</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>339</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>148</v>
-      </c>
+        <v>354</v>
+      </c>
+      <c r="N39" s="2"/>
+      <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>80</v>
       </c>
@@ -6681,19 +6711,19 @@
         <v>80</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>340</v>
+        <v>355</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>143</v>
+        <v>102</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>80</v>
@@ -6713,10 +6743,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6727,7 +6757,7 @@
         <v>90</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>80</v>
@@ -6739,13 +6769,13 @@
         <v>91</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>182</v>
+        <v>329</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6772,13 +6802,13 @@
         <v>80</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>289</v>
+        <v>80</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>354</v>
+        <v>80</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>355</v>
+        <v>80</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>80</v>
@@ -6796,13 +6826,13 @@
         <v>80</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>90</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>80</v>
@@ -6828,10 +6858,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6839,7 +6869,7 @@
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="G41" t="s" s="2">
         <v>90</v>
@@ -6851,20 +6881,18 @@
         <v>80</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>357</v>
+        <v>202</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>358</v>
+        <v>161</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>359</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>360</v>
-      </c>
+        <v>162</v>
+      </c>
+      <c r="N41" s="2"/>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>80</v>
@@ -6913,19 +6941,19 @@
         <v>80</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>356</v>
+        <v>163</v>
       </c>
       <c r="AG41" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="AH41" t="s" s="2">
         <v>90</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>80</v>
+        <v>164</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>102</v>
+        <v>80</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>80</v>
@@ -6937,7 +6965,7 @@
         <v>80</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>80</v>
+        <v>165</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>80</v>
@@ -6945,21 +6973,21 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>80</v>
+        <v>137</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>80</v>
@@ -6968,21 +6996,21 @@
         <v>80</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>362</v>
+        <v>138</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>363</v>
+        <v>139</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="N42" s="2"/>
-      <c r="O42" t="s" s="2">
-        <v>365</v>
-      </c>
+        <v>167</v>
+      </c>
+      <c r="N42" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>80</v>
       </c>
@@ -7030,19 +7058,19 @@
         <v>80</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>361</v>
+        <v>171</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>102</v>
+        <v>143</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>80</v>
@@ -7051,10 +7079,10 @@
         <v>80</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>333</v>
+        <v>80</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>366</v>
+        <v>165</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>80</v>
@@ -7062,42 +7090,46 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>367</v>
+        <v>361</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>367</v>
+        <v>361</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>80</v>
+        <v>337</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I43" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="J43" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>368</v>
+        <v>138</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>369</v>
+        <v>338</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>370</v>
-      </c>
-      <c r="N43" s="2"/>
-      <c r="O43" s="2"/>
+        <v>339</v>
+      </c>
+      <c r="N43" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="O43" t="s" s="2">
+        <v>148</v>
+      </c>
       <c r="P43" t="s" s="2">
         <v>80</v>
       </c>
@@ -7145,42 +7177,42 @@
         <v>80</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>367</v>
+        <v>340</v>
       </c>
       <c r="AG43" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>102</v>
+        <v>143</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>371</v>
+        <v>80</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>372</v>
+        <v>80</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>373</v>
+        <v>80</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>374</v>
+        <v>144</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>375</v>
+        <v>80</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>376</v>
+        <v>362</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>376</v>
+        <v>362</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7188,7 +7220,7 @@
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="G44" t="s" s="2">
         <v>90</v>
@@ -7200,16 +7232,16 @@
         <v>80</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>92</v>
+        <v>182</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>161</v>
+        <v>363</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>162</v>
+        <v>364</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -7236,13 +7268,13 @@
         <v>80</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>80</v>
+        <v>289</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>80</v>
+        <v>365</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>80</v>
+        <v>366</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>80</v>
@@ -7260,19 +7292,19 @@
         <v>80</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>163</v>
+        <v>362</v>
       </c>
       <c r="AG44" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="AH44" t="s" s="2">
         <v>90</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>164</v>
+        <v>80</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>80</v>
+        <v>102</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>80</v>
@@ -7284,7 +7316,7 @@
         <v>80</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>165</v>
+        <v>80</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>80</v>
@@ -7292,21 +7324,21 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>377</v>
+        <v>367</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>377</v>
+        <v>367</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>137</v>
+        <v>80</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>80</v>
@@ -7315,19 +7347,19 @@
         <v>80</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>138</v>
+        <v>368</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>139</v>
+        <v>369</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>167</v>
+        <v>370</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>141</v>
+        <v>371</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -7365,31 +7397,31 @@
         <v>80</v>
       </c>
       <c r="AB45" t="s" s="2">
-        <v>168</v>
+        <v>80</v>
       </c>
       <c r="AC45" t="s" s="2">
-        <v>169</v>
+        <v>80</v>
       </c>
       <c r="AD45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE45" t="s" s="2">
-        <v>170</v>
+        <v>80</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>171</v>
+        <v>367</v>
       </c>
       <c r="AG45" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>143</v>
+        <v>102</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>80</v>
@@ -7401,7 +7433,7 @@
         <v>80</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>165</v>
+        <v>80</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>80</v>
@@ -7409,10 +7441,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>378</v>
+        <v>372</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>378</v>
+        <v>372</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7435,18 +7467,18 @@
         <v>91</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>202</v>
+        <v>373</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="O46" s="2"/>
+        <v>375</v>
+      </c>
+      <c r="N46" s="2"/>
+      <c r="O46" t="s" s="2">
+        <v>376</v>
+      </c>
       <c r="P46" t="s" s="2">
         <v>80</v>
       </c>
@@ -7494,7 +7526,7 @@
         <v>80</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>382</v>
+        <v>372</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -7503,7 +7535,7 @@
         <v>90</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>383</v>
+        <v>80</v>
       </c>
       <c r="AJ46" t="s" s="2">
         <v>102</v>
@@ -7515,10 +7547,10 @@
         <v>80</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>80</v>
+        <v>333</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>144</v>
+        <v>377</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>80</v>
@@ -7526,10 +7558,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>384</v>
+        <v>378</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>384</v>
+        <v>378</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7537,7 +7569,7 @@
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="G47" t="s" s="2">
         <v>90</v>
@@ -7552,17 +7584,15 @@
         <v>91</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>104</v>
+        <v>379</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>387</v>
-      </c>
+        <v>381</v>
+      </c>
+      <c r="N47" s="2"/>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>80</v>
@@ -7587,13 +7617,13 @@
         <v>80</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>187</v>
+        <v>80</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>388</v>
+        <v>80</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>389</v>
+        <v>80</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>80</v>
@@ -7611,10 +7641,10 @@
         <v>80</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>390</v>
+        <v>378</v>
       </c>
       <c r="AG47" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="AH47" t="s" s="2">
         <v>90</v>
@@ -7626,27 +7656,27 @@
         <v>102</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>80</v>
+        <v>382</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>80</v>
+        <v>383</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>80</v>
+        <v>384</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>144</v>
+        <v>385</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>80</v>
+        <v>386</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7654,7 +7684,7 @@
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="G48" t="s" s="2">
         <v>90</v>
@@ -7666,20 +7696,18 @@
         <v>80</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>151</v>
+        <v>92</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>392</v>
+        <v>161</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>393</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>394</v>
-      </c>
+        <v>162</v>
+      </c>
+      <c r="N48" s="2"/>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>80</v>
@@ -7728,7 +7756,7 @@
         <v>80</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>395</v>
+        <v>163</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -7737,10 +7765,10 @@
         <v>90</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>396</v>
+        <v>164</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>102</v>
+        <v>80</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>80</v>
@@ -7752,7 +7780,7 @@
         <v>80</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>80</v>
@@ -7760,21 +7788,21 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>397</v>
+        <v>388</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>397</v>
+        <v>388</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>80</v>
+        <v>137</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>80</v>
@@ -7786,15 +7814,17 @@
         <v>80</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>92</v>
+        <v>138</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>161</v>
+        <v>139</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="N49" s="2"/>
+        <v>167</v>
+      </c>
+      <c r="N49" t="s" s="2">
+        <v>141</v>
+      </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>80</v>
@@ -7831,31 +7861,31 @@
         <v>80</v>
       </c>
       <c r="AB49" t="s" s="2">
-        <v>80</v>
+        <v>168</v>
       </c>
       <c r="AC49" t="s" s="2">
-        <v>80</v>
+        <v>169</v>
       </c>
       <c r="AD49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE49" t="s" s="2">
-        <v>80</v>
+        <v>170</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>164</v>
+        <v>80</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>80</v>
+        <v>143</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>80</v>
@@ -7875,21 +7905,21 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>398</v>
+        <v>389</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>398</v>
+        <v>389</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>137</v>
+        <v>80</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>80</v>
@@ -7898,19 +7928,19 @@
         <v>80</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>138</v>
+        <v>202</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>139</v>
+        <v>390</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>167</v>
+        <v>391</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>141</v>
+        <v>392</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -7948,31 +7978,31 @@
         <v>80</v>
       </c>
       <c r="AB50" t="s" s="2">
-        <v>168</v>
+        <v>80</v>
       </c>
       <c r="AC50" t="s" s="2">
-        <v>169</v>
+        <v>80</v>
       </c>
       <c r="AD50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE50" t="s" s="2">
-        <v>170</v>
+        <v>80</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>171</v>
+        <v>393</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>80</v>
+        <v>394</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>143</v>
+        <v>102</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>80</v>
@@ -7984,7 +8014,7 @@
         <v>80</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>165</v>
+        <v>144</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>80</v>
@@ -7992,10 +8022,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8012,26 +8042,24 @@
         <v>80</v>
       </c>
       <c r="I51" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="J51" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>173</v>
+        <v>396</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>174</v>
+        <v>397</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>176</v>
-      </c>
+        <v>398</v>
+      </c>
+      <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>80</v>
       </c>
@@ -8055,13 +8083,13 @@
         <v>80</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>114</v>
+        <v>187</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>177</v>
+        <v>399</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>178</v>
+        <v>400</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>80</v>
@@ -8079,7 +8107,7 @@
         <v>80</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>179</v>
+        <v>401</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
@@ -8100,10 +8128,10 @@
         <v>80</v>
       </c>
       <c r="AM51" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN51" t="s" s="2">
         <v>144</v>
-      </c>
-      <c r="AN51" t="s" s="2">
-        <v>180</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>80</v>
@@ -8111,10 +8139,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8122,7 +8150,7 @@
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="G52" t="s" s="2">
         <v>90</v>
@@ -8137,20 +8165,18 @@
         <v>91</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>182</v>
+        <v>151</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>183</v>
+        <v>403</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>184</v>
+        <v>404</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>185</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>186</v>
-      </c>
+        <v>405</v>
+      </c>
+      <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>80</v>
       </c>
@@ -8174,13 +8200,13 @@
         <v>80</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>187</v>
+        <v>80</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>188</v>
+        <v>80</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>189</v>
+        <v>80</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>80</v>
@@ -8198,7 +8224,7 @@
         <v>80</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>190</v>
+        <v>406</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
@@ -8207,7 +8233,7 @@
         <v>90</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>80</v>
+        <v>407</v>
       </c>
       <c r="AJ52" t="s" s="2">
         <v>102</v>
@@ -8219,10 +8245,10 @@
         <v>80</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>191</v>
+        <v>80</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>180</v>
+        <v>158</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>80</v>
@@ -8230,10 +8256,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>401</v>
+        <v>408</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>401</v>
+        <v>408</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8241,7 +8267,7 @@
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="G53" t="s" s="2">
         <v>90</v>
@@ -8253,23 +8279,19 @@
         <v>80</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>193</v>
+        <v>161</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>194</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="O53" t="s" s="2">
-        <v>196</v>
-      </c>
+        <v>162</v>
+      </c>
+      <c r="N53" s="2"/>
+      <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>80</v>
       </c>
@@ -8281,7 +8303,7 @@
         <v>80</v>
       </c>
       <c r="T53" t="s" s="2">
-        <v>197</v>
+        <v>80</v>
       </c>
       <c r="U53" t="s" s="2">
         <v>80</v>
@@ -8293,11 +8315,13 @@
         <v>80</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="Y53" s="2"/>
+        <v>80</v>
+      </c>
+      <c r="Y53" t="s" s="2">
+        <v>80</v>
+      </c>
       <c r="Z53" t="s" s="2">
-        <v>402</v>
+        <v>80</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>80</v>
@@ -8315,7 +8339,7 @@
         <v>80</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>198</v>
+        <v>163</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -8324,10 +8348,10 @@
         <v>90</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>80</v>
+        <v>164</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>102</v>
+        <v>80</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>80</v>
@@ -8336,10 +8360,10 @@
         <v>80</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>199</v>
+        <v>80</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>200</v>
+        <v>165</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>80</v>
@@ -8347,21 +8371,21 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>403</v>
+        <v>409</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>403</v>
+        <v>409</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>80</v>
+        <v>137</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>80</v>
@@ -8370,19 +8394,19 @@
         <v>80</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>202</v>
+        <v>138</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>203</v>
+        <v>139</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>204</v>
+        <v>167</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>205</v>
+        <v>141</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8396,7 +8420,7 @@
         <v>80</v>
       </c>
       <c r="T54" t="s" s="2">
-        <v>206</v>
+        <v>80</v>
       </c>
       <c r="U54" t="s" s="2">
         <v>80</v>
@@ -8420,31 +8444,31 @@
         <v>80</v>
       </c>
       <c r="AB54" t="s" s="2">
-        <v>80</v>
+        <v>168</v>
       </c>
       <c r="AC54" t="s" s="2">
-        <v>80</v>
+        <v>169</v>
       </c>
       <c r="AD54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE54" t="s" s="2">
-        <v>80</v>
+        <v>170</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>207</v>
+        <v>171</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>208</v>
+        <v>80</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>102</v>
+        <v>143</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>80</v>
@@ -8453,10 +8477,10 @@
         <v>80</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>209</v>
+        <v>80</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>210</v>
+        <v>165</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>80</v>
@@ -8464,10 +8488,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>404</v>
+        <v>410</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>404</v>
+        <v>410</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8484,22 +8508,26 @@
         <v>80</v>
       </c>
       <c r="I55" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="J55" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>212</v>
+        <v>110</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>213</v>
+        <v>173</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>214</v>
-      </c>
-      <c r="N55" s="2"/>
-      <c r="O55" s="2"/>
+        <v>174</v>
+      </c>
+      <c r="N55" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="O55" t="s" s="2">
+        <v>176</v>
+      </c>
       <c r="P55" t="s" s="2">
         <v>80</v>
       </c>
@@ -8523,13 +8551,13 @@
         <v>80</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>80</v>
+        <v>114</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>80</v>
+        <v>177</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>80</v>
+        <v>178</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>80</v>
@@ -8547,7 +8575,7 @@
         <v>80</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>215</v>
+        <v>179</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
@@ -8568,10 +8596,10 @@
         <v>80</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>216</v>
+        <v>144</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>217</v>
+        <v>180</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>80</v>
@@ -8579,10 +8607,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>405</v>
+        <v>411</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>405</v>
+        <v>411</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8605,18 +8633,20 @@
         <v>91</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>219</v>
+        <v>182</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>220</v>
+        <v>183</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>221</v>
+        <v>184</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="O56" s="2"/>
+        <v>185</v>
+      </c>
+      <c r="O56" t="s" s="2">
+        <v>186</v>
+      </c>
       <c r="P56" t="s" s="2">
         <v>80</v>
       </c>
@@ -8640,13 +8670,13 @@
         <v>80</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>80</v>
+        <v>187</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>80</v>
+        <v>188</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>80</v>
+        <v>189</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>80</v>
@@ -8664,7 +8694,7 @@
         <v>80</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>223</v>
+        <v>190</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
@@ -8685,10 +8715,10 @@
         <v>80</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>224</v>
+        <v>191</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>225</v>
+        <v>180</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>80</v>
@@ -8696,10 +8726,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8707,7 +8737,7 @@
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="G57" t="s" s="2">
         <v>90</v>
@@ -8722,18 +8752,20 @@
         <v>91</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>202</v>
+        <v>104</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>407</v>
+        <v>193</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>408</v>
+        <v>194</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>409</v>
-      </c>
-      <c r="O57" s="2"/>
+        <v>195</v>
+      </c>
+      <c r="O57" t="s" s="2">
+        <v>196</v>
+      </c>
       <c r="P57" t="s" s="2">
         <v>80</v>
       </c>
@@ -8745,7 +8777,7 @@
         <v>80</v>
       </c>
       <c r="T57" t="s" s="2">
-        <v>80</v>
+        <v>197</v>
       </c>
       <c r="U57" t="s" s="2">
         <v>80</v>
@@ -8757,13 +8789,11 @@
         <v>80</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y57" t="s" s="2">
-        <v>80</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="Y57" s="2"/>
       <c r="Z57" t="s" s="2">
-        <v>80</v>
+        <v>413</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>80</v>
@@ -8781,7 +8811,7 @@
         <v>80</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>410</v>
+        <v>198</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
@@ -8790,7 +8820,7 @@
         <v>90</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>396</v>
+        <v>80</v>
       </c>
       <c r="AJ57" t="s" s="2">
         <v>102</v>
@@ -8802,10 +8832,10 @@
         <v>80</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>80</v>
+        <v>199</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>144</v>
+        <v>200</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>80</v>
@@ -8813,10 +8843,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8824,10 +8854,10 @@
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>80</v>
@@ -8839,15 +8869,17 @@
         <v>91</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>412</v>
+        <v>202</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>413</v>
+        <v>203</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="N58" s="2"/>
+        <v>204</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>205</v>
+      </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>80</v>
@@ -8860,7 +8892,7 @@
         <v>80</v>
       </c>
       <c r="T58" t="s" s="2">
-        <v>80</v>
+        <v>206</v>
       </c>
       <c r="U58" t="s" s="2">
         <v>80</v>
@@ -8896,16 +8928,16 @@
         <v>80</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>411</v>
+        <v>207</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>80</v>
+        <v>208</v>
       </c>
       <c r="AJ58" t="s" s="2">
         <v>102</v>
@@ -8914,13 +8946,13 @@
         <v>80</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>372</v>
+        <v>80</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>80</v>
+        <v>209</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>415</v>
+        <v>210</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>80</v>
@@ -8928,14 +8960,14 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>417</v>
+        <v>80</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
@@ -8954,13 +8986,13 @@
         <v>91</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>418</v>
+        <v>212</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>419</v>
+        <v>213</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>420</v>
+        <v>214</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -9011,7 +9043,7 @@
         <v>80</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>416</v>
+        <v>215</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
@@ -9026,35 +9058,35 @@
         <v>102</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>421</v>
+        <v>80</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>422</v>
+        <v>80</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>423</v>
+        <v>216</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>424</v>
+        <v>217</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>425</v>
+        <v>80</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>426</v>
+        <v>416</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>426</v>
+        <v>416</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>427</v>
+        <v>80</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="G60" t="s" s="2">
         <v>90</v>
@@ -9069,15 +9101,17 @@
         <v>91</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>428</v>
+        <v>220</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>429</v>
-      </c>
-      <c r="N60" s="2"/>
+        <v>221</v>
+      </c>
+      <c r="N60" t="s" s="2">
+        <v>222</v>
+      </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>80</v>
@@ -9126,7 +9160,7 @@
         <v>80</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>426</v>
+        <v>223</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
@@ -9141,27 +9175,27 @@
         <v>102</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>430</v>
+        <v>80</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>431</v>
+        <v>80</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>432</v>
+        <v>224</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>433</v>
+        <v>225</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>434</v>
+        <v>80</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>435</v>
+        <v>417</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>435</v>
+        <v>417</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9184,15 +9218,17 @@
         <v>91</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>436</v>
+        <v>202</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>437</v>
+        <v>418</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="N61" s="2"/>
+        <v>419</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>420</v>
+      </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>80</v>
@@ -9217,13 +9253,13 @@
         <v>80</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>289</v>
+        <v>80</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>439</v>
+        <v>80</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>440</v>
+        <v>80</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>80</v>
@@ -9241,7 +9277,7 @@
         <v>80</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>435</v>
+        <v>421</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
@@ -9250,7 +9286,7 @@
         <v>90</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>80</v>
+        <v>407</v>
       </c>
       <c r="AJ61" t="s" s="2">
         <v>102</v>
@@ -9265,29 +9301,29 @@
         <v>80</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>441</v>
+        <v>144</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>442</v>
+        <v>80</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>443</v>
+        <v>422</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>443</v>
+        <v>422</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>444</v>
+        <v>80</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>80</v>
@@ -9299,13 +9335,13 @@
         <v>91</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>445</v>
+        <v>423</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>446</v>
+        <v>424</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>447</v>
+        <v>425</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9356,13 +9392,13 @@
         <v>80</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>443</v>
+        <v>422</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>80</v>
@@ -9371,35 +9407,35 @@
         <v>102</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>448</v>
+        <v>80</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>449</v>
+        <v>383</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>450</v>
+        <v>80</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>451</v>
+        <v>426</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>452</v>
+        <v>80</v>
       </c>
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>453</v>
+        <v>427</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>453</v>
+        <v>427</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>454</v>
+        <v>428</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="G63" t="s" s="2">
         <v>90</v>
@@ -9414,17 +9450,15 @@
         <v>91</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>455</v>
+        <v>429</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>456</v>
+        <v>430</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>457</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>458</v>
-      </c>
+        <v>431</v>
+      </c>
+      <c r="N63" s="2"/>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>80</v>
@@ -9473,7 +9507,7 @@
         <v>80</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>453</v>
+        <v>427</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>78</v>
@@ -9488,35 +9522,35 @@
         <v>102</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>459</v>
+        <v>432</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>460</v>
+        <v>433</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>461</v>
+        <v>434</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>462</v>
+        <v>435</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>463</v>
+        <v>436</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>464</v>
+        <v>437</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>464</v>
+        <v>437</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>465</v>
+        <v>438</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="G64" t="s" s="2">
         <v>90</v>
@@ -9531,17 +9565,15 @@
         <v>91</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>182</v>
+        <v>212</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>466</v>
+        <v>439</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>467</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>468</v>
-      </c>
+        <v>440</v>
+      </c>
+      <c r="N64" s="2"/>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>80</v>
@@ -9566,13 +9598,13 @@
         <v>80</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>289</v>
+        <v>80</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>469</v>
+        <v>80</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>470</v>
+        <v>80</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>80</v>
@@ -9590,7 +9622,7 @@
         <v>80</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>464</v>
+        <v>437</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>78</v>
@@ -9605,38 +9637,38 @@
         <v>102</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>471</v>
+        <v>441</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>472</v>
+        <v>442</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>473</v>
+        <v>443</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>474</v>
+        <v>444</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>80</v>
+        <v>445</v>
       </c>
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>475</v>
+        <v>446</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>475</v>
+        <v>446</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>476</v>
+        <v>80</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>80</v>
@@ -9648,17 +9680,15 @@
         <v>91</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>477</v>
+        <v>447</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>478</v>
+        <v>448</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>479</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>480</v>
-      </c>
+        <v>449</v>
+      </c>
+      <c r="N65" s="2"/>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>80</v>
@@ -9683,13 +9713,13 @@
         <v>80</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>80</v>
+        <v>289</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>80</v>
+        <v>450</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>80</v>
+        <v>451</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>80</v>
@@ -9707,13 +9737,13 @@
         <v>80</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>475</v>
+        <v>446</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>80</v>
@@ -9722,38 +9752,38 @@
         <v>102</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>481</v>
+        <v>80</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>472</v>
+        <v>80</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>482</v>
+        <v>80</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>483</v>
+        <v>452</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>80</v>
+        <v>453</v>
       </c>
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>484</v>
+        <v>454</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>484</v>
+        <v>454</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>80</v>
+        <v>455</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>80</v>
@@ -9765,13 +9795,13 @@
         <v>91</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>485</v>
+        <v>456</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>486</v>
+        <v>457</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>487</v>
+        <v>458</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -9798,13 +9828,13 @@
         <v>80</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>289</v>
+        <v>80</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>488</v>
+        <v>80</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>489</v>
+        <v>80</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>80</v>
@@ -9822,13 +9852,13 @@
         <v>80</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>484</v>
+        <v>454</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>80</v>
@@ -9837,38 +9867,38 @@
         <v>102</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>80</v>
+        <v>459</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>472</v>
+        <v>460</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>80</v>
+        <v>461</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>490</v>
+        <v>462</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>80</v>
+        <v>463</v>
       </c>
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>491</v>
+        <v>464</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>491</v>
+        <v>464</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>80</v>
+        <v>465</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>80</v>
@@ -9880,16 +9910,16 @@
         <v>91</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>492</v>
+        <v>466</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>493</v>
+        <v>467</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>494</v>
+        <v>468</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>495</v>
+        <v>469</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -9915,13 +9945,13 @@
         <v>80</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>289</v>
+        <v>80</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>496</v>
+        <v>80</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>497</v>
+        <v>80</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>80</v>
@@ -9939,13 +9969,13 @@
         <v>80</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>491</v>
+        <v>464</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>80</v>
@@ -9954,38 +9984,38 @@
         <v>102</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>498</v>
+        <v>470</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>499</v>
+        <v>471</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>500</v>
+        <v>472</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>501</v>
+        <v>473</v>
       </c>
       <c r="AO67" t="s" s="2">
-        <v>80</v>
+        <v>474</v>
       </c>
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>502</v>
+        <v>475</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>502</v>
+        <v>475</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>80</v>
+        <v>476</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>80</v>
@@ -9994,18 +10024,20 @@
         <v>80</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>503</v>
+        <v>182</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>504</v>
+        <v>477</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>505</v>
-      </c>
-      <c r="N68" s="2"/>
+        <v>478</v>
+      </c>
+      <c r="N68" t="s" s="2">
+        <v>479</v>
+      </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>80</v>
@@ -10030,13 +10062,13 @@
         <v>80</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>80</v>
+        <v>289</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>80</v>
+        <v>480</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>80</v>
+        <v>481</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>80</v>
@@ -10054,13 +10086,13 @@
         <v>80</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>502</v>
+        <v>475</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>80</v>
@@ -10069,16 +10101,16 @@
         <v>102</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>506</v>
+        <v>482</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>80</v>
+        <v>483</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>507</v>
+        <v>484</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>508</v>
+        <v>485</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>80</v>
@@ -10086,14 +10118,14 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>509</v>
+        <v>486</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>509</v>
+        <v>486</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>510</v>
+        <v>487</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
@@ -10109,19 +10141,19 @@
         <v>80</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>511</v>
+        <v>488</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>512</v>
+        <v>489</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>513</v>
+        <v>490</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>514</v>
+        <v>491</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -10171,7 +10203,7 @@
         <v>80</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>509</v>
+        <v>486</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>78</v>
@@ -10186,16 +10218,16 @@
         <v>102</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>515</v>
+        <v>492</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>80</v>
+        <v>483</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>516</v>
+        <v>493</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>517</v>
+        <v>494</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>80</v>
@@ -10203,10 +10235,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>518</v>
+        <v>495</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>518</v>
+        <v>495</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10229,17 +10261,15 @@
         <v>91</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>519</v>
+        <v>496</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>520</v>
+        <v>497</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>521</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>522</v>
-      </c>
+        <v>498</v>
+      </c>
+      <c r="N70" s="2"/>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>80</v>
@@ -10264,13 +10294,13 @@
         <v>80</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>80</v>
+        <v>289</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>80</v>
+        <v>499</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>80</v>
+        <v>500</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>80</v>
@@ -10288,7 +10318,7 @@
         <v>80</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>518</v>
+        <v>495</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>78</v>
@@ -10306,13 +10336,13 @@
         <v>80</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>80</v>
+        <v>483</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>523</v>
+        <v>80</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>524</v>
+        <v>501</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>80</v>
@@ -10320,14 +10350,14 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>525</v>
+        <v>502</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>525</v>
+        <v>502</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>526</v>
+        <v>80</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
@@ -10346,20 +10376,18 @@
         <v>91</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>182</v>
+        <v>503</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>527</v>
+        <v>504</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>528</v>
+        <v>505</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>529</v>
-      </c>
-      <c r="O71" t="s" s="2">
-        <v>530</v>
-      </c>
+        <v>506</v>
+      </c>
+      <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
         <v>80</v>
       </c>
@@ -10386,10 +10414,10 @@
         <v>289</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>531</v>
+        <v>507</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>532</v>
+        <v>508</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>80</v>
@@ -10407,7 +10435,7 @@
         <v>80</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>525</v>
+        <v>502</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>78</v>
@@ -10416,44 +10444,44 @@
         <v>79</v>
       </c>
       <c r="AI71" t="s" s="2">
-        <v>533</v>
+        <v>80</v>
       </c>
       <c r="AJ71" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>80</v>
+        <v>509</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>80</v>
+        <v>510</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>523</v>
+        <v>511</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>534</v>
+        <v>512</v>
       </c>
       <c r="AO71" t="s" s="2">
-        <v>535</v>
+        <v>80</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>536</v>
+        <v>513</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>536</v>
+        <v>513</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>537</v>
+        <v>80</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>80</v>
@@ -10462,21 +10490,19 @@
         <v>80</v>
       </c>
       <c r="J72" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>538</v>
+        <v>514</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>539</v>
+        <v>515</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>528</v>
+        <v>516</v>
       </c>
       <c r="N72" s="2"/>
-      <c r="O72" t="s" s="2">
-        <v>530</v>
-      </c>
+      <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
         <v>80</v>
       </c>
@@ -10524,46 +10550,46 @@
         <v>80</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>536</v>
+        <v>513</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AI72" t="s" s="2">
-        <v>533</v>
+        <v>80</v>
       </c>
       <c r="AJ72" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>80</v>
+        <v>517</v>
       </c>
       <c r="AL72" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>523</v>
+        <v>518</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>534</v>
+        <v>519</v>
       </c>
       <c r="AO72" t="s" s="2">
-        <v>540</v>
+        <v>80</v>
       </c>
     </row>
-    <row r="73">
+    <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>541</v>
+        <v>520</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>541</v>
+        <v>520</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>80</v>
+        <v>521</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
@@ -10573,7 +10599,7 @@
         <v>79</v>
       </c>
       <c r="H73" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="I73" t="s" s="2">
         <v>80</v>
@@ -10582,15 +10608,17 @@
         <v>80</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>542</v>
+        <v>522</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>49</v>
+        <v>523</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>543</v>
-      </c>
-      <c r="N73" s="2"/>
+        <v>524</v>
+      </c>
+      <c r="N73" t="s" s="2">
+        <v>525</v>
+      </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
         <v>80</v>
@@ -10639,7 +10667,7 @@
         <v>80</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>541</v>
+        <v>520</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>78</v>
@@ -10654,27 +10682,27 @@
         <v>102</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>544</v>
+        <v>526</v>
       </c>
       <c r="AL73" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>333</v>
+        <v>527</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>545</v>
+        <v>528</v>
       </c>
       <c r="AO73" t="s" s="2">
-        <v>546</v>
+        <v>80</v>
       </c>
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>547</v>
+        <v>529</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>547</v>
+        <v>529</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10694,18 +10722,20 @@
         <v>80</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>329</v>
+        <v>530</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>548</v>
+        <v>531</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>549</v>
-      </c>
-      <c r="N74" s="2"/>
+        <v>532</v>
+      </c>
+      <c r="N74" t="s" s="2">
+        <v>533</v>
+      </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
         <v>80</v>
@@ -10754,7 +10784,7 @@
         <v>80</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>547</v>
+        <v>529</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>78</v>
@@ -10775,10 +10805,10 @@
         <v>80</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>333</v>
+        <v>534</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>550</v>
+        <v>535</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>80</v>
@@ -10786,21 +10816,21 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>551</v>
+        <v>536</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>551</v>
+        <v>536</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>80</v>
+        <v>537</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>80</v>
@@ -10809,19 +10839,23 @@
         <v>80</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>202</v>
+        <v>182</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>161</v>
+        <v>538</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="N75" s="2"/>
-      <c r="O75" s="2"/>
+        <v>539</v>
+      </c>
+      <c r="N75" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="O75" t="s" s="2">
+        <v>541</v>
+      </c>
       <c r="P75" t="s" s="2">
         <v>80</v>
       </c>
@@ -10845,13 +10879,13 @@
         <v>80</v>
       </c>
       <c r="X75" t="s" s="2">
-        <v>80</v>
+        <v>289</v>
       </c>
       <c r="Y75" t="s" s="2">
-        <v>80</v>
+        <v>542</v>
       </c>
       <c r="Z75" t="s" s="2">
-        <v>80</v>
+        <v>543</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>80</v>
@@ -10869,19 +10903,19 @@
         <v>80</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>163</v>
+        <v>536</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>164</v>
+        <v>544</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>80</v>
+        <v>102</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>80</v>
@@ -10890,32 +10924,32 @@
         <v>80</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>80</v>
+        <v>534</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>165</v>
+        <v>545</v>
       </c>
       <c r="AO75" t="s" s="2">
-        <v>80</v>
+        <v>546</v>
       </c>
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>552</v>
+        <v>547</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>552</v>
+        <v>547</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>137</v>
+        <v>548</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="H76" t="s" s="2">
         <v>80</v>
@@ -10924,21 +10958,21 @@
         <v>80</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>138</v>
+        <v>549</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>139</v>
+        <v>550</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="N76" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="O76" s="2"/>
+        <v>539</v>
+      </c>
+      <c r="N76" s="2"/>
+      <c r="O76" t="s" s="2">
+        <v>541</v>
+      </c>
       <c r="P76" t="s" s="2">
         <v>80</v>
       </c>
@@ -10986,19 +11020,19 @@
         <v>80</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>171</v>
+        <v>547</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AI76" t="s" s="2">
-        <v>80</v>
+        <v>544</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>143</v>
+        <v>102</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>80</v>
@@ -11007,25 +11041,25 @@
         <v>80</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>80</v>
+        <v>534</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>165</v>
+        <v>545</v>
       </c>
       <c r="AO76" t="s" s="2">
-        <v>80</v>
+        <v>551</v>
       </c>
     </row>
-    <row r="77" hidden="true">
+    <row r="77">
       <c r="A77" t="s" s="2">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>337</v>
+        <v>80</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
@@ -11035,29 +11069,25 @@
         <v>79</v>
       </c>
       <c r="H77" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="I77" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="J77" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>138</v>
+        <v>553</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>338</v>
+        <v>49</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>339</v>
-      </c>
-      <c r="N77" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="O77" t="s" s="2">
-        <v>148</v>
-      </c>
+        <v>554</v>
+      </c>
+      <c r="N77" s="2"/>
+      <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
         <v>80</v>
       </c>
@@ -11105,7 +11135,7 @@
         <v>80</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>340</v>
+        <v>552</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>78</v>
@@ -11117,30 +11147,30 @@
         <v>80</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>143</v>
+        <v>102</v>
       </c>
       <c r="AK77" t="s" s="2">
-        <v>80</v>
+        <v>555</v>
       </c>
       <c r="AL77" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>80</v>
+        <v>333</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>144</v>
+        <v>556</v>
       </c>
       <c r="AO77" t="s" s="2">
-        <v>80</v>
+        <v>557</v>
       </c>
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11151,7 +11181,7 @@
         <v>78</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>80</v>
@@ -11160,16 +11190,16 @@
         <v>80</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>555</v>
+        <v>329</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>548</v>
+        <v>559</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>549</v>
+        <v>560</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -11220,13 +11250,13 @@
         <v>80</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AI78" t="s" s="2">
         <v>80</v>
@@ -11244,7 +11274,7 @@
         <v>333</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>550</v>
+        <v>561</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>80</v>
@@ -11252,10 +11282,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>556</v>
+        <v>562</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>556</v>
+        <v>562</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11266,7 +11296,7 @@
         <v>78</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="H79" t="s" s="2">
         <v>80</v>
@@ -11278,17 +11308,15 @@
         <v>80</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>557</v>
+        <v>202</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>558</v>
+        <v>161</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>559</v>
-      </c>
-      <c r="N79" t="s" s="2">
-        <v>560</v>
-      </c>
+        <v>162</v>
+      </c>
+      <c r="N79" s="2"/>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
         <v>80</v>
@@ -11337,38 +11365,506 @@
         <v>80</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>556</v>
+        <v>163</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH79" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI79" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="AJ79" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AK79" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL79" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM79" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN79" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="AO79" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="80" hidden="true">
+      <c r="A80" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="B80" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="C80" s="2"/>
+      <c r="D80" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="E80" s="2"/>
+      <c r="F80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G80" t="s" s="2">
         <v>79</v>
       </c>
-      <c r="AI79" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ79" t="s" s="2">
+      <c r="H80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K80" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="L80" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="M80" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="N80" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="O80" s="2"/>
+      <c r="P80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q80" s="2"/>
+      <c r="R80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF80" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="AG80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH80" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ80" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="AK80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN80" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="AO80" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="81" hidden="true">
+      <c r="A81" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="B81" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="C81" s="2"/>
+      <c r="D81" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="E81" s="2"/>
+      <c r="F81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G81" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H81" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I81" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="J81" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K81" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="L81" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="M81" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="N81" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="O81" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="P81" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q81" s="2"/>
+      <c r="R81" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S81" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T81" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U81" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V81" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W81" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X81" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y81" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z81" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA81" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB81" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC81" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD81" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE81" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF81" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="AG81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH81" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI81" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ81" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="AK81" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL81" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM81" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN81" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="AO81" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="82" hidden="true">
+      <c r="A82" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="B82" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="C82" s="2"/>
+      <c r="D82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E82" s="2"/>
+      <c r="F82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G82" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J82" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K82" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="L82" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="M82" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="N82" s="2"/>
+      <c r="O82" s="2"/>
+      <c r="P82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q82" s="2"/>
+      <c r="R82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF82" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="AG82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH82" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ82" t="s" s="2">
         <v>102</v>
       </c>
-      <c r="AK79" t="s" s="2">
+      <c r="AK82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM82" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="AN82" t="s" s="2">
         <v>561</v>
       </c>
-      <c r="AL79" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM79" t="s" s="2">
+      <c r="AO82" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="83" hidden="true">
+      <c r="A83" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="B83" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="C83" s="2"/>
+      <c r="D83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E83" s="2"/>
+      <c r="F83" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G83" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K83" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="L83" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="M83" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="N83" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="O83" s="2"/>
+      <c r="P83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q83" s="2"/>
+      <c r="R83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF83" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="AG83" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH83" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ83" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK83" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="AL83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM83" t="s" s="2">
         <v>144</v>
       </c>
-      <c r="AN79" t="s" s="2">
-        <v>562</v>
-      </c>
-      <c r="AO79" t="s" s="2">
+      <c r="AN83" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="AO83" t="s" s="2">
         <v>80</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO79">
+  <autoFilter ref="A1:AO83">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -11378,7 +11874,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI78">
+  <conditionalFormatting sqref="A2:AI82">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/currentbuild/StructureDefinition-parek-service-request.xlsx
+++ b/currentbuild/StructureDefinition-parek-service-request.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.1.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-19T07:57:25+00:00</t>
+    <t>2026-03-19T11:47:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/StructureDefinition-parek-service-request.xlsx
+++ b/currentbuild/StructureDefinition-parek-service-request.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.1</t>
+    <t>0.1.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-19T11:47:55+00:00</t>
+    <t>2026-03-20T10:04:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/StructureDefinition-parek-service-request.xlsx
+++ b/currentbuild/StructureDefinition-parek-service-request.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-20T10:04:21+00:00</t>
+    <t>2026-03-20T11:14:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/StructureDefinition-parek-service-request.xlsx
+++ b/currentbuild/StructureDefinition-parek-service-request.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-20T11:14:53+00:00</t>
+    <t>2026-03-20T11:25:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/StructureDefinition-parek-service-request.xlsx
+++ b/currentbuild/StructureDefinition-parek-service-request.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-20T11:25:24+00:00</t>
+    <t>2026-03-20T11:48:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/StructureDefinition-parek-service-request.xlsx
+++ b/currentbuild/StructureDefinition-parek-service-request.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.2</t>
+    <t>0.1.3</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-20T11:48:45+00:00</t>
+    <t>2026-03-20T12:42:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/StructureDefinition-parek-service-request.xlsx
+++ b/currentbuild/StructureDefinition-parek-service-request.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-20T12:42:40+00:00</t>
+    <t>2026-03-20T12:57:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/StructureDefinition-parek-service-request.xlsx
+++ b/currentbuild/StructureDefinition-parek-service-request.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-20T12:57:31+00:00</t>
+    <t>2026-03-20T13:17:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1307,7 +1307,7 @@
     <t>ServiceRequest.subject.identifier.system</t>
   </si>
   <si>
-    <t>http://hl7.no/fhir/ig/ParekIG/ValueSet/public-it-type-vs</t>
+    <t>http://hl7.no/fhir/ig/ParekIG/ValueSet/public-id-type-vs</t>
   </si>
   <si>
     <t>ServiceRequest.subject.identifier.value</t>

--- a/currentbuild/StructureDefinition-parek-service-request.xlsx
+++ b/currentbuild/StructureDefinition-parek-service-request.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$83</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$85</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3096" uniqueCount="574">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3171" uniqueCount="590">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.3</t>
+    <t>0.1.4</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-20T13:17:08+00:00</t>
+    <t>2026-04-10T11:25:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -500,6 +500,13 @@
     <t>The identifier.type element is used to distinguish between the identifiers assigned by the orderer (known as the 'Placer' in HL7 V2) and the producer of the observations in response to the order (known as the 'Filler' in HL7 V2).  For further discussion and examples see the resource notes section below.</t>
   </si>
   <si>
+    <t xml:space="preserve">value:system}
+</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
     <t>Request.identifier</t>
   </si>
   <si>
@@ -513,6 +520,18 @@
   </si>
   <si>
     <t>ClinicalStatement.identifier</t>
+  </si>
+  <si>
+    <t>ServiceRequest.identifier:RequesterDefinedUuid</t>
+  </si>
+  <si>
+    <t>RequesterDefinedUuid</t>
+  </si>
+  <si>
+    <t>External system creating a ServiceRequst must provide a unique identifier for idem potency (to avoid duplicates).</t>
+  </si>
+  <si>
+    <t>ServiceRequest.identifier:RequesterDefinedUuid.id</t>
   </si>
   <si>
     <t>ServiceRequest.identifier.id</t>
@@ -534,6 +553,9 @@
     <t>n/a</t>
   </si>
   <si>
+    <t>ServiceRequest.identifier:RequesterDefinedUuid.extension</t>
+  </si>
+  <si>
     <t>ServiceRequest.identifier.extension</t>
   </si>
   <si>
@@ -547,12 +569,12 @@
     <t>Extensions are always sliced by (at least) url</t>
   </si>
   <si>
-    <t>open</t>
-  </si>
-  <si>
     <t>Element.extension</t>
   </si>
   <si>
+    <t>ServiceRequest.identifier:RequesterDefinedUuid.use</t>
+  </si>
+  <si>
     <t>ServiceRequest.identifier.use</t>
   </si>
   <si>
@@ -578,6 +600,9 @@
   </si>
   <si>
     <t>Role.code or implied by context</t>
+  </si>
+  <si>
+    <t>ServiceRequest.identifier:RequesterDefinedUuid.type</t>
   </si>
   <si>
     <t>ServiceRequest.identifier.type</t>
@@ -614,6 +639,9 @@
     <t>CX.5</t>
   </si>
   <si>
+    <t>ServiceRequest.identifier:RequesterDefinedUuid.system</t>
+  </si>
+  <si>
     <t>ServiceRequest.identifier.system</t>
   </si>
   <si>
@@ -629,6 +657,9 @@
     <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
   </si>
   <si>
+    <t>http://hl7.no/fhir/ig/ParekIG/NamingSystem/RequesterDefinedUuid</t>
+  </si>
+  <si>
     <t>http://www.acme.com/identifiers/patient</t>
   </si>
   <si>
@@ -639,6 +670,9 @@
   </si>
   <si>
     <t>II.root or Role.id.root</t>
+  </si>
+  <si>
+    <t>ServiceRequest.identifier:RequesterDefinedUuid.value</t>
   </si>
   <si>
     <t>ServiceRequest.identifier.value</t>
@@ -673,6 +707,9 @@
     <t>II.extension or II.root if system indicates OID or GUID (Or Role.id.extension or root)</t>
   </si>
   <si>
+    <t>ServiceRequest.identifier:RequesterDefinedUuid.period</t>
+  </si>
+  <si>
     <t>ServiceRequest.identifier.period</t>
   </si>
   <si>
@@ -695,6 +732,9 @@
     <t>Role.effectiveTime or implied by context</t>
   </si>
   <si>
+    <t>ServiceRequest.identifier:RequesterDefinedUuid.assigner</t>
+  </si>
+  <si>
     <t>ServiceRequest.identifier.assigner</t>
   </si>
   <si>
@@ -718,6 +758,15 @@
   </si>
   <si>
     <t>II.assigningAuthorityName but note that this is an improper use by the definition of the field.  Also Role.scoper</t>
+  </si>
+  <si>
+    <t>ServiceRequest.identifier:LocalId</t>
+  </si>
+  <si>
+    <t>LocalId</t>
+  </si>
+  <si>
+    <t>Identifiers assigned to this order instance by the orderer and/or the receiver and/or order fulfiller.</t>
   </si>
   <si>
     <t>ServiceRequest.instantiatesCanonical</t>
@@ -2129,12 +2178,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO83"/>
+  <dimension ref="A1:AO85"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="46.05078125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="47.2109375" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="46.05078125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="18.671875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="37.7265625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
@@ -3425,16 +3474,14 @@
         <v>80</v>
       </c>
       <c r="AB11" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC11" t="s" s="2">
-        <v>80</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="AC11" s="2"/>
       <c r="AD11" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE11" t="s" s="2">
-        <v>80</v>
+        <v>156</v>
       </c>
       <c r="AF11" t="s" s="2">
         <v>150</v>
@@ -3452,35 +3499,37 @@
         <v>102</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="AO11" t="s" s="2">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="C12" s="2"/>
+        <v>150</v>
+      </c>
+      <c r="C12" t="s" s="2">
+        <v>163</v>
+      </c>
       <c r="D12" t="s" s="2">
         <v>80</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="G12" t="s" s="2">
         <v>90</v>
@@ -3492,18 +3541,20 @@
         <v>80</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>92</v>
+        <v>151</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>161</v>
+        <v>152</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="N12" s="2"/>
+        <v>164</v>
+      </c>
+      <c r="N12" t="s" s="2">
+        <v>154</v>
+      </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
         <v>80</v>
@@ -3552,53 +3603,53 @@
         <v>80</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>163</v>
+        <v>150</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>164</v>
+        <v>80</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>80</v>
+        <v>102</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>80</v>
+        <v>157</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>80</v>
+        <v>158</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>80</v>
+        <v>159</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="AO12" t="s" s="2">
-        <v>80</v>
+        <v>161</v>
       </c>
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B13" t="s" s="2">
         <v>166</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>137</v>
+        <v>80</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>80</v>
@@ -3610,17 +3661,15 @@
         <v>80</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>138</v>
+        <v>92</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>139</v>
+        <v>167</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>141</v>
-      </c>
+        <v>168</v>
+      </c>
+      <c r="N13" s="2"/>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
         <v>80</v>
@@ -3657,43 +3706,43 @@
         <v>80</v>
       </c>
       <c r="AB13" t="s" s="2">
-        <v>168</v>
+        <v>80</v>
       </c>
       <c r="AC13" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD13" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE13" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF13" t="s" s="2">
         <v>169</v>
       </c>
-      <c r="AD13" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE13" t="s" s="2">
+      <c r="AG13" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH13" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI13" t="s" s="2">
         <v>170</v>
       </c>
-      <c r="AF13" t="s" s="2">
+      <c r="AJ13" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AK13" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL13" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM13" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN13" t="s" s="2">
         <v>171</v>
-      </c>
-      <c r="AG13" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH13" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI13" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ13" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="AK13" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL13" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM13" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN13" t="s" s="2">
-        <v>165</v>
       </c>
       <c r="AO13" t="s" s="2">
         <v>80</v>
@@ -3704,43 +3753,41 @@
         <v>172</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>80</v>
+        <v>137</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>110</v>
+        <v>138</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>173</v>
+        <v>139</v>
       </c>
       <c r="M14" t="s" s="2">
         <v>174</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="O14" t="s" s="2">
-        <v>176</v>
-      </c>
+        <v>141</v>
+      </c>
+      <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
         <v>80</v>
       </c>
@@ -3764,43 +3811,43 @@
         <v>80</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>114</v>
+        <v>80</v>
       </c>
       <c r="Y14" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z14" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA14" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB14" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="AC14" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="AD14" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE14" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="AF14" t="s" s="2">
         <v>177</v>
       </c>
-      <c r="Z14" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="AA14" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB14" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC14" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD14" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE14" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF14" t="s" s="2">
-        <v>179</v>
-      </c>
       <c r="AG14" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>102</v>
+        <v>143</v>
       </c>
       <c r="AK14" t="s" s="2">
         <v>80</v>
@@ -3809,10 +3856,10 @@
         <v>80</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>144</v>
+        <v>80</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>180</v>
+        <v>171</v>
       </c>
       <c r="AO14" t="s" s="2">
         <v>80</v>
@@ -3820,10 +3867,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3840,25 +3887,25 @@
         <v>80</v>
       </c>
       <c r="I15" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="J15" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K15" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="L15" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="M15" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="N15" t="s" s="2">
         <v>182</v>
       </c>
-      <c r="L15" t="s" s="2">
+      <c r="O15" t="s" s="2">
         <v>183</v>
-      </c>
-      <c r="M15" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="N15" t="s" s="2">
-        <v>185</v>
-      </c>
-      <c r="O15" t="s" s="2">
-        <v>186</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>80</v>
@@ -3883,13 +3930,13 @@
         <v>80</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>187</v>
+        <v>114</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>80</v>
@@ -3907,7 +3954,7 @@
         <v>80</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>78</v>
@@ -3928,10 +3975,10 @@
         <v>80</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>191</v>
+        <v>144</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="AO15" t="s" s="2">
         <v>80</v>
@@ -3939,10 +3986,10 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3950,7 +3997,7 @@
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="G16" t="s" s="2">
         <v>90</v>
@@ -3965,19 +4012,19 @@
         <v>91</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>104</v>
+        <v>190</v>
       </c>
       <c r="L16" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="M16" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="N16" t="s" s="2">
         <v>193</v>
       </c>
-      <c r="M16" t="s" s="2">
+      <c r="O16" t="s" s="2">
         <v>194</v>
-      </c>
-      <c r="N16" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="O16" t="s" s="2">
-        <v>196</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>80</v>
@@ -3990,25 +4037,25 @@
         <v>80</v>
       </c>
       <c r="T16" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U16" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V16" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W16" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X16" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="Y16" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="Z16" t="s" s="2">
         <v>197</v>
-      </c>
-      <c r="U16" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V16" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W16" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X16" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y16" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z16" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>80</v>
@@ -4050,7 +4097,7 @@
         <v>199</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>200</v>
+        <v>187</v>
       </c>
       <c r="AO16" t="s" s="2">
         <v>80</v>
@@ -4058,7 +4105,7 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B17" t="s" s="2">
         <v>201</v>
@@ -4084,18 +4131,20 @@
         <v>91</v>
       </c>
       <c r="K17" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="L17" t="s" s="2">
         <v>202</v>
       </c>
-      <c r="L17" t="s" s="2">
+      <c r="M17" t="s" s="2">
         <v>203</v>
       </c>
-      <c r="M17" t="s" s="2">
+      <c r="N17" t="s" s="2">
         <v>204</v>
       </c>
-      <c r="N17" t="s" s="2">
+      <c r="O17" t="s" s="2">
         <v>205</v>
       </c>
-      <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>80</v>
       </c>
@@ -4104,10 +4153,10 @@
         <v>80</v>
       </c>
       <c r="S17" t="s" s="2">
-        <v>80</v>
+        <v>206</v>
       </c>
       <c r="T17" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="U17" t="s" s="2">
         <v>80</v>
@@ -4143,7 +4192,7 @@
         <v>80</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>78</v>
@@ -4152,7 +4201,7 @@
         <v>90</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>208</v>
+        <v>80</v>
       </c>
       <c r="AJ17" t="s" s="2">
         <v>102</v>
@@ -4178,7 +4227,7 @@
         <v>211</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4186,7 +4235,7 @@
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="G18" t="s" s="2">
         <v>90</v>
@@ -4201,15 +4250,17 @@
         <v>91</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>214</v>
-      </c>
-      <c r="N18" s="2"/>
+        <v>215</v>
+      </c>
+      <c r="N18" t="s" s="2">
+        <v>216</v>
+      </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>80</v>
@@ -4222,7 +4273,7 @@
         <v>80</v>
       </c>
       <c r="T18" t="s" s="2">
-        <v>80</v>
+        <v>217</v>
       </c>
       <c r="U18" t="s" s="2">
         <v>80</v>
@@ -4258,7 +4309,7 @@
         <v>80</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
@@ -4267,7 +4318,7 @@
         <v>90</v>
       </c>
       <c r="AI18" t="s" s="2">
-        <v>80</v>
+        <v>219</v>
       </c>
       <c r="AJ18" t="s" s="2">
         <v>102</v>
@@ -4279,10 +4330,10 @@
         <v>80</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>80</v>
@@ -4290,10 +4341,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4316,17 +4367,15 @@
         <v>91</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>222</v>
-      </c>
+        <v>226</v>
+      </c>
+      <c r="N19" s="2"/>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>80</v>
@@ -4375,7 +4424,7 @@
         <v>80</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
@@ -4396,10 +4445,10 @@
         <v>80</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>80</v>
@@ -4407,10 +4456,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4421,7 +4470,7 @@
         <v>78</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>80</v>
@@ -4433,16 +4482,16 @@
         <v>91</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -4492,13 +4541,13 @@
         <v>80</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>80</v>
@@ -4507,29 +4556,31 @@
         <v>102</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>231</v>
+        <v>80</v>
       </c>
       <c r="AL20" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>80</v>
       </c>
     </row>
-    <row r="21" hidden="true">
+    <row r="21">
       <c r="A21" t="s" s="2">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="C21" s="2"/>
+        <v>150</v>
+      </c>
+      <c r="C21" t="s" s="2">
+        <v>240</v>
+      </c>
       <c r="D21" t="s" s="2">
         <v>80</v>
       </c>
@@ -4541,7 +4592,7 @@
         <v>79</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="I21" t="s" s="2">
         <v>80</v>
@@ -4550,16 +4601,16 @@
         <v>91</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>104</v>
+        <v>151</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>235</v>
+        <v>152</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>237</v>
+        <v>154</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4609,7 +4660,7 @@
         <v>80</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>234</v>
+        <v>150</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
@@ -4624,31 +4675,31 @@
         <v>102</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>238</v>
+        <v>157</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>80</v>
+        <v>158</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>232</v>
+        <v>159</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>233</v>
+        <v>160</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>80</v>
+        <v>161</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>240</v>
+        <v>80</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
@@ -4667,15 +4718,17 @@
         <v>91</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>243</v>
-      </c>
-      <c r="N22" s="2"/>
+        <v>245</v>
+      </c>
+      <c r="N22" t="s" s="2">
+        <v>246</v>
+      </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>80</v>
@@ -4724,7 +4777,7 @@
         <v>80</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
@@ -4739,16 +4792,16 @@
         <v>102</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>80</v>
@@ -4756,14 +4809,14 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>248</v>
+        <v>80</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
@@ -4782,15 +4835,17 @@
         <v>91</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>249</v>
+        <v>104</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="N23" s="2"/>
+        <v>252</v>
+      </c>
+      <c r="N23" t="s" s="2">
+        <v>253</v>
+      </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>80</v>
@@ -4839,7 +4894,7 @@
         <v>80</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -4854,16 +4909,16 @@
         <v>102</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>80</v>
@@ -4885,7 +4940,7 @@
         <v>78</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>80</v>
@@ -4897,20 +4952,16 @@
         <v>91</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>151</v>
+        <v>257</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>258</v>
-      </c>
-      <c r="N24" t="s" s="2">
         <v>259</v>
       </c>
-      <c r="O24" t="s" s="2">
-        <v>260</v>
-      </c>
+      <c r="N24" s="2"/>
+      <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>80</v>
       </c>
@@ -4964,7 +5015,7 @@
         <v>78</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>80</v>
@@ -4973,16 +5024,16 @@
         <v>102</v>
       </c>
       <c r="AK24" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="AL24" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM24" t="s" s="2">
         <v>261</v>
       </c>
-      <c r="AL24" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM24" t="s" s="2">
+      <c r="AN24" t="s" s="2">
         <v>262</v>
-      </c>
-      <c r="AN24" t="s" s="2">
-        <v>263</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>80</v>
@@ -4990,43 +5041,41 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>80</v>
+        <v>264</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I25" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="J25" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>110</v>
+        <v>265</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="N25" t="s" s="2">
         <v>267</v>
       </c>
+      <c r="N25" s="2"/>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>80</v>
@@ -5051,13 +5100,13 @@
         <v>80</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>114</v>
+        <v>80</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>268</v>
+        <v>80</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>269</v>
+        <v>80</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>80</v>
@@ -5075,13 +5124,13 @@
         <v>80</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>80</v>
@@ -5090,35 +5139,35 @@
         <v>102</v>
       </c>
       <c r="AK25" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="AL25" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM25" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="AN25" t="s" s="2">
         <v>270</v>
       </c>
-      <c r="AL25" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="AM25" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="AN25" t="s" s="2">
-        <v>273</v>
-      </c>
       <c r="AO25" t="s" s="2">
-        <v>274</v>
+        <v>80</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>80</v>
+        <v>272</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="G26" t="s" s="2">
         <v>90</v>
@@ -5127,24 +5176,26 @@
         <v>80</v>
       </c>
       <c r="I26" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="J26" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>110</v>
+        <v>151</v>
       </c>
       <c r="L26" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="M26" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="N26" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="O26" t="s" s="2">
         <v>276</v>
       </c>
-      <c r="M26" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>278</v>
-      </c>
-      <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>80</v>
       </c>
@@ -5168,13 +5219,13 @@
         <v>80</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>114</v>
+        <v>80</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>279</v>
+        <v>80</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>280</v>
+        <v>80</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>80</v>
@@ -5192,10 +5243,10 @@
         <v>80</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="AH26" t="s" s="2">
         <v>90</v>
@@ -5207,16 +5258,16 @@
         <v>102</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>282</v>
+        <v>80</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>144</v>
+        <v>278</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>80</v>
@@ -5224,10 +5275,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5235,35 +5286,33 @@
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I27" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="J27" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>182</v>
+        <v>110</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>288</v>
-      </c>
+        <v>283</v>
+      </c>
+      <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>80</v>
       </c>
@@ -5287,13 +5336,13 @@
         <v>80</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>289</v>
+        <v>114</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>290</v>
+        <v>284</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>80</v>
@@ -5311,13 +5360,13 @@
         <v>80</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="AG27" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>80</v>
@@ -5326,27 +5375,27 @@
         <v>102</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>80</v>
+        <v>286</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>80</v>
+        <v>290</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5354,7 +5403,7 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="G28" t="s" s="2">
         <v>90</v>
@@ -5363,7 +5412,7 @@
         <v>80</v>
       </c>
       <c r="I28" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="J28" t="s" s="2">
         <v>91</v>
@@ -5372,19 +5421,19 @@
         <v>110</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="N28" s="2"/>
+        <v>293</v>
+      </c>
+      <c r="N28" t="s" s="2">
+        <v>294</v>
+      </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>80</v>
       </c>
-      <c r="Q28" t="s" s="2">
-        <v>297</v>
-      </c>
+      <c r="Q28" s="2"/>
       <c r="R28" t="s" s="2">
         <v>80</v>
       </c>
@@ -5407,10 +5456,10 @@
         <v>114</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>80</v>
@@ -5428,10 +5477,10 @@
         <v>80</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="AH28" t="s" s="2">
         <v>90</v>
@@ -5443,16 +5492,16 @@
         <v>102</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>302</v>
+        <v>144</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>80</v>
@@ -5460,10 +5509,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5474,65 +5523,63 @@
         <v>78</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I29" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="J29" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K29" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="L29" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="M29" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="N29" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="O29" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="P29" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q29" s="2"/>
+      <c r="R29" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S29" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T29" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U29" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V29" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W29" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X29" t="s" s="2">
         <v>305</v>
       </c>
-      <c r="L29" t="s" s="2">
+      <c r="Y29" t="s" s="2">
         <v>306</v>
       </c>
-      <c r="M29" t="s" s="2">
+      <c r="Z29" t="s" s="2">
         <v>307</v>
       </c>
-      <c r="N29" t="s" s="2">
-        <v>308</v>
-      </c>
-      <c r="O29" t="s" s="2">
-        <v>309</v>
-      </c>
-      <c r="P29" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q29" t="s" s="2">
-        <v>310</v>
-      </c>
-      <c r="R29" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S29" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T29" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U29" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V29" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W29" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X29" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y29" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z29" t="s" s="2">
-        <v>80</v>
-      </c>
       <c r="AA29" t="s" s="2">
         <v>80</v>
       </c>
@@ -5549,13 +5596,13 @@
         <v>80</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>80</v>
@@ -5564,31 +5611,31 @@
         <v>102</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>311</v>
+        <v>80</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>80</v>
+        <v>298</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>80</v>
+        <v>308</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>80</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>314</v>
+        <v>80</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
@@ -5598,7 +5645,7 @@
         <v>90</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="I30" t="s" s="2">
         <v>80</v>
@@ -5607,22 +5654,22 @@
         <v>91</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>315</v>
+        <v>110</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>317</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>318</v>
-      </c>
+        <v>312</v>
+      </c>
+      <c r="N30" s="2"/>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>80</v>
       </c>
-      <c r="Q30" s="2"/>
+      <c r="Q30" t="s" s="2">
+        <v>313</v>
+      </c>
       <c r="R30" t="s" s="2">
         <v>80</v>
       </c>
@@ -5642,13 +5689,13 @@
         <v>80</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>289</v>
+        <v>114</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>80</v>
@@ -5666,7 +5713,7 @@
         <v>80</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -5675,71 +5722,75 @@
         <v>90</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>321</v>
+        <v>80</v>
       </c>
       <c r="AJ30" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>326</v>
+        <v>80</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>328</v>
+        <v>80</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I31" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="J31" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>329</v>
+        <v>321</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>330</v>
+        <v>322</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>331</v>
+        <v>323</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>332</v>
-      </c>
-      <c r="O31" s="2"/>
+        <v>324</v>
+      </c>
+      <c r="O31" t="s" s="2">
+        <v>325</v>
+      </c>
       <c r="P31" t="s" s="2">
         <v>80</v>
       </c>
-      <c r="Q31" s="2"/>
+      <c r="Q31" t="s" s="2">
+        <v>326</v>
+      </c>
       <c r="R31" t="s" s="2">
         <v>80</v>
       </c>
@@ -5783,46 +5834,46 @@
         <v>80</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>321</v>
+        <v>80</v>
       </c>
       <c r="AJ31" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>80</v>
+        <v>327</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>333</v>
+        <v>80</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>80</v>
+        <v>328</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>80</v>
       </c>
     </row>
-    <row r="32" hidden="true">
+    <row r="32">
       <c r="A32" t="s" s="2">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>80</v>
+        <v>330</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -5832,24 +5883,26 @@
         <v>90</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>202</v>
+        <v>331</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>161</v>
+        <v>332</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="N32" s="2"/>
+        <v>333</v>
+      </c>
+      <c r="N32" t="s" s="2">
+        <v>334</v>
+      </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>80</v>
@@ -5874,13 +5927,13 @@
         <v>80</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>80</v>
+        <v>305</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>80</v>
+        <v>335</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>80</v>
+        <v>336</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>80</v>
@@ -5898,7 +5951,7 @@
         <v>80</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>163</v>
+        <v>329</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -5907,41 +5960,41 @@
         <v>90</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>164</v>
+        <v>337</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>80</v>
+        <v>102</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>80</v>
+        <v>338</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>80</v>
+        <v>339</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>80</v>
+        <v>340</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>165</v>
+        <v>341</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>80</v>
+        <v>342</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>335</v>
+        <v>343</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>335</v>
+        <v>343</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>137</v>
+        <v>344</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="G33" t="s" s="2">
         <v>79</v>
@@ -5953,19 +6006,19 @@
         <v>80</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>138</v>
+        <v>345</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>139</v>
+        <v>346</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>167</v>
+        <v>347</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>141</v>
+        <v>348</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -6015,7 +6068,7 @@
         <v>80</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>171</v>
+        <v>343</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -6024,10 +6077,10 @@
         <v>79</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>80</v>
+        <v>337</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>143</v>
+        <v>102</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>80</v>
@@ -6036,10 +6089,10 @@
         <v>80</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>80</v>
+        <v>349</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>165</v>
+        <v>80</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>80</v>
@@ -6047,46 +6100,42 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>336</v>
+        <v>350</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>336</v>
+        <v>350</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>337</v>
+        <v>80</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I34" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>138</v>
+        <v>213</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>338</v>
+        <v>167</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>339</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="O34" t="s" s="2">
-        <v>148</v>
-      </c>
+        <v>168</v>
+      </c>
+      <c r="N34" s="2"/>
+      <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>80</v>
       </c>
@@ -6134,19 +6183,19 @@
         <v>80</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>340</v>
+        <v>169</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>80</v>
+        <v>170</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>143</v>
+        <v>80</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>80</v>
@@ -6158,7 +6207,7 @@
         <v>80</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>144</v>
+        <v>171</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>80</v>
@@ -6166,21 +6215,21 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>341</v>
+        <v>351</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>341</v>
+        <v>351</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>80</v>
+        <v>137</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>80</v>
@@ -6192,15 +6241,17 @@
         <v>80</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>342</v>
+        <v>138</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>343</v>
+        <v>139</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>344</v>
-      </c>
-      <c r="N35" s="2"/>
+        <v>174</v>
+      </c>
+      <c r="N35" t="s" s="2">
+        <v>141</v>
+      </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>80</v>
@@ -6249,19 +6300,19 @@
         <v>80</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>341</v>
+        <v>177</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>102</v>
+        <v>143</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>80</v>
@@ -6273,7 +6324,7 @@
         <v>80</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>80</v>
+        <v>171</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>80</v>
@@ -6281,42 +6332,46 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>345</v>
+        <v>352</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>345</v>
+        <v>352</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>80</v>
+        <v>353</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I36" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>92</v>
+        <v>138</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>161</v>
+        <v>354</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="N36" s="2"/>
-      <c r="O36" s="2"/>
+        <v>355</v>
+      </c>
+      <c r="N36" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="O36" t="s" s="2">
+        <v>148</v>
+      </c>
       <c r="P36" t="s" s="2">
         <v>80</v>
       </c>
@@ -6364,19 +6419,19 @@
         <v>80</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>163</v>
+        <v>356</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>164</v>
+        <v>80</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>80</v>
+        <v>143</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>80</v>
@@ -6388,7 +6443,7 @@
         <v>80</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>165</v>
+        <v>144</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>80</v>
@@ -6396,21 +6451,21 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>346</v>
+        <v>357</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>346</v>
+        <v>357</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>137</v>
+        <v>80</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>80</v>
@@ -6422,17 +6477,15 @@
         <v>80</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>138</v>
+        <v>358</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>139</v>
+        <v>359</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>141</v>
-      </c>
+        <v>360</v>
+      </c>
+      <c r="N37" s="2"/>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>80</v>
@@ -6469,31 +6522,31 @@
         <v>80</v>
       </c>
       <c r="AB37" t="s" s="2">
-        <v>168</v>
+        <v>80</v>
       </c>
       <c r="AC37" t="s" s="2">
-        <v>169</v>
+        <v>80</v>
       </c>
       <c r="AD37" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE37" t="s" s="2">
-        <v>170</v>
+        <v>80</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>171</v>
+        <v>357</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>143</v>
+        <v>102</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>80</v>
@@ -6505,7 +6558,7 @@
         <v>80</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>165</v>
+        <v>80</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>80</v>
@@ -6513,10 +6566,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>347</v>
+        <v>361</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>347</v>
+        <v>361</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6524,7 +6577,7 @@
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="G38" t="s" s="2">
         <v>90</v>
@@ -6536,16 +6589,16 @@
         <v>80</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>182</v>
+        <v>92</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>348</v>
+        <v>167</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>349</v>
+        <v>168</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -6596,7 +6649,7 @@
         <v>80</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>350</v>
+        <v>169</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -6605,10 +6658,10 @@
         <v>90</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>80</v>
+        <v>170</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>102</v>
+        <v>80</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>80</v>
@@ -6620,7 +6673,7 @@
         <v>80</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>144</v>
+        <v>171</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>80</v>
@@ -6628,21 +6681,21 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>351</v>
+        <v>362</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>351</v>
+        <v>362</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>80</v>
+        <v>137</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>80</v>
@@ -6651,18 +6704,20 @@
         <v>80</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>352</v>
+        <v>138</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>353</v>
+        <v>139</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>354</v>
-      </c>
-      <c r="N39" s="2"/>
+        <v>174</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>141</v>
+      </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>80</v>
@@ -6699,31 +6754,31 @@
         <v>80</v>
       </c>
       <c r="AB39" t="s" s="2">
-        <v>80</v>
+        <v>175</v>
       </c>
       <c r="AC39" t="s" s="2">
-        <v>80</v>
+        <v>176</v>
       </c>
       <c r="AD39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE39" t="s" s="2">
-        <v>80</v>
+        <v>156</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>355</v>
+        <v>177</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>102</v>
+        <v>143</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>80</v>
@@ -6735,7 +6790,7 @@
         <v>80</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>144</v>
+        <v>171</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>80</v>
@@ -6743,10 +6798,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6757,7 +6812,7 @@
         <v>90</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>80</v>
@@ -6769,13 +6824,13 @@
         <v>91</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>329</v>
+        <v>190</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>358</v>
+        <v>365</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6826,13 +6881,13 @@
         <v>80</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>356</v>
+        <v>366</v>
       </c>
       <c r="AG40" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>80</v>
@@ -6850,7 +6905,7 @@
         <v>80</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>80</v>
+        <v>144</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>80</v>
@@ -6858,10 +6913,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6881,16 +6936,16 @@
         <v>80</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>202</v>
+        <v>368</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>161</v>
+        <v>369</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>162</v>
+        <v>370</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6941,7 +6996,7 @@
         <v>80</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>163</v>
+        <v>371</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
@@ -6950,10 +7005,10 @@
         <v>90</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>164</v>
+        <v>80</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>80</v>
+        <v>102</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>80</v>
@@ -6965,7 +7020,7 @@
         <v>80</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>165</v>
+        <v>144</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>80</v>
@@ -6973,18 +7028,18 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>360</v>
+        <v>372</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>360</v>
+        <v>372</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>137</v>
+        <v>80</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="G42" t="s" s="2">
         <v>79</v>
@@ -6996,20 +7051,18 @@
         <v>80</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>138</v>
+        <v>345</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>139</v>
+        <v>373</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>141</v>
-      </c>
+        <v>374</v>
+      </c>
+      <c r="N42" s="2"/>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>80</v>
@@ -7058,10 +7111,10 @@
         <v>80</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>171</v>
+        <v>372</v>
       </c>
       <c r="AG42" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="AH42" t="s" s="2">
         <v>79</v>
@@ -7070,7 +7123,7 @@
         <v>80</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>143</v>
+        <v>102</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>80</v>
@@ -7082,7 +7135,7 @@
         <v>80</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>165</v>
+        <v>80</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>80</v>
@@ -7090,46 +7143,42 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>361</v>
+        <v>375</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>361</v>
+        <v>375</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>337</v>
+        <v>80</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I43" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>138</v>
+        <v>213</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>338</v>
+        <v>167</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>339</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="O43" t="s" s="2">
-        <v>148</v>
-      </c>
+        <v>168</v>
+      </c>
+      <c r="N43" s="2"/>
+      <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>80</v>
       </c>
@@ -7177,19 +7226,19 @@
         <v>80</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>340</v>
+        <v>169</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>80</v>
+        <v>170</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>143</v>
+        <v>80</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>80</v>
@@ -7201,7 +7250,7 @@
         <v>80</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>144</v>
+        <v>171</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>80</v>
@@ -7209,21 +7258,21 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>362</v>
+        <v>376</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>362</v>
+        <v>376</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>80</v>
+        <v>137</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>80</v>
@@ -7232,18 +7281,20 @@
         <v>80</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>182</v>
+        <v>138</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>363</v>
+        <v>139</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="N44" s="2"/>
+        <v>174</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>141</v>
+      </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>80</v>
@@ -7268,13 +7319,13 @@
         <v>80</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>289</v>
+        <v>80</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>365</v>
+        <v>80</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>366</v>
+        <v>80</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>80</v>
@@ -7292,19 +7343,19 @@
         <v>80</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>362</v>
+        <v>177</v>
       </c>
       <c r="AG44" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>102</v>
+        <v>143</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>80</v>
@@ -7316,7 +7367,7 @@
         <v>80</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>80</v>
+        <v>171</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>80</v>
@@ -7324,44 +7375,46 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>367</v>
+        <v>377</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>367</v>
+        <v>377</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>80</v>
+        <v>353</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I45" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="J45" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>368</v>
+        <v>138</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>369</v>
+        <v>354</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>370</v>
+        <v>355</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>371</v>
-      </c>
-      <c r="O45" s="2"/>
+        <v>141</v>
+      </c>
+      <c r="O45" t="s" s="2">
+        <v>148</v>
+      </c>
       <c r="P45" t="s" s="2">
         <v>80</v>
       </c>
@@ -7409,19 +7462,19 @@
         <v>80</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>367</v>
+        <v>356</v>
       </c>
       <c r="AG45" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>102</v>
+        <v>143</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>80</v>
@@ -7433,7 +7486,7 @@
         <v>80</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>80</v>
+        <v>144</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>80</v>
@@ -7441,10 +7494,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7452,7 +7505,7 @@
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="G46" t="s" s="2">
         <v>90</v>
@@ -7467,18 +7520,16 @@
         <v>91</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>373</v>
+        <v>190</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="N46" s="2"/>
-      <c r="O46" t="s" s="2">
-        <v>376</v>
-      </c>
+      <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>80</v>
       </c>
@@ -7502,13 +7553,13 @@
         <v>80</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>80</v>
+        <v>305</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>80</v>
+        <v>381</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>80</v>
+        <v>382</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>80</v>
@@ -7526,10 +7577,10 @@
         <v>80</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="AG46" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="AH46" t="s" s="2">
         <v>90</v>
@@ -7547,10 +7598,10 @@
         <v>80</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>333</v>
+        <v>80</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>377</v>
+        <v>80</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>80</v>
@@ -7558,10 +7609,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7584,15 +7635,17 @@
         <v>91</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="N47" s="2"/>
+        <v>386</v>
+      </c>
+      <c r="N47" t="s" s="2">
+        <v>387</v>
+      </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>80</v>
@@ -7641,7 +7694,7 @@
         <v>80</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>90</v>
@@ -7656,27 +7709,27 @@
         <v>102</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>382</v>
+        <v>80</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>383</v>
+        <v>80</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>384</v>
+        <v>80</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>385</v>
+        <v>80</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>386</v>
+        <v>80</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7696,19 +7749,21 @@
         <v>80</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>92</v>
+        <v>389</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>161</v>
+        <v>390</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>162</v>
+        <v>391</v>
       </c>
       <c r="N48" s="2"/>
-      <c r="O48" s="2"/>
+      <c r="O48" t="s" s="2">
+        <v>392</v>
+      </c>
       <c r="P48" t="s" s="2">
         <v>80</v>
       </c>
@@ -7756,7 +7811,7 @@
         <v>80</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>163</v>
+        <v>388</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -7765,10 +7820,10 @@
         <v>90</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>164</v>
+        <v>80</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>80</v>
+        <v>102</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>80</v>
@@ -7777,10 +7832,10 @@
         <v>80</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>80</v>
+        <v>349</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>165</v>
+        <v>393</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>80</v>
@@ -7788,21 +7843,21 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>388</v>
+        <v>394</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>388</v>
+        <v>394</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>137</v>
+        <v>80</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>80</v>
@@ -7811,20 +7866,18 @@
         <v>80</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>138</v>
+        <v>395</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>139</v>
+        <v>396</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>141</v>
-      </c>
+        <v>397</v>
+      </c>
+      <c r="N49" s="2"/>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>80</v>
@@ -7861,54 +7914,54 @@
         <v>80</v>
       </c>
       <c r="AB49" t="s" s="2">
-        <v>168</v>
+        <v>80</v>
       </c>
       <c r="AC49" t="s" s="2">
-        <v>169</v>
+        <v>80</v>
       </c>
       <c r="AD49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE49" t="s" s="2">
-        <v>170</v>
+        <v>80</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>171</v>
+        <v>394</v>
       </c>
       <c r="AG49" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>143</v>
+        <v>102</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>80</v>
+        <v>398</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>80</v>
+        <v>399</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>80</v>
+        <v>400</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>165</v>
+        <v>401</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>80</v>
+        <v>402</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>389</v>
+        <v>403</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>389</v>
+        <v>403</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7928,20 +7981,18 @@
         <v>80</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>202</v>
+        <v>92</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>390</v>
+        <v>167</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>391</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>392</v>
-      </c>
+        <v>168</v>
+      </c>
+      <c r="N50" s="2"/>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>80</v>
@@ -7990,7 +8041,7 @@
         <v>80</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>393</v>
+        <v>169</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
@@ -7999,10 +8050,10 @@
         <v>90</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>394</v>
+        <v>170</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>102</v>
+        <v>80</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>80</v>
@@ -8014,7 +8065,7 @@
         <v>80</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>144</v>
+        <v>171</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>80</v>
@@ -8022,21 +8073,21 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>395</v>
+        <v>404</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>395</v>
+        <v>404</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>80</v>
+        <v>137</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>80</v>
@@ -8045,19 +8096,19 @@
         <v>80</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>104</v>
+        <v>138</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>396</v>
+        <v>139</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>397</v>
+        <v>174</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>398</v>
+        <v>141</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -8083,43 +8134,43 @@
         <v>80</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>187</v>
+        <v>80</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>399</v>
+        <v>80</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>400</v>
+        <v>80</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AB51" t="s" s="2">
-        <v>80</v>
+        <v>175</v>
       </c>
       <c r="AC51" t="s" s="2">
-        <v>80</v>
+        <v>176</v>
       </c>
       <c r="AD51" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE51" t="s" s="2">
-        <v>80</v>
+        <v>156</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>401</v>
+        <v>177</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>102</v>
+        <v>143</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>80</v>
@@ -8131,7 +8182,7 @@
         <v>80</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>144</v>
+        <v>171</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>80</v>
@@ -8139,10 +8190,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8150,7 +8201,7 @@
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="G52" t="s" s="2">
         <v>90</v>
@@ -8165,16 +8216,16 @@
         <v>91</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>151</v>
+        <v>213</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -8224,7 +8275,7 @@
         <v>80</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
@@ -8233,7 +8284,7 @@
         <v>90</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="AJ52" t="s" s="2">
         <v>102</v>
@@ -8248,7 +8299,7 @@
         <v>80</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>158</v>
+        <v>144</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>80</v>
@@ -8256,10 +8307,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8279,18 +8330,20 @@
         <v>80</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>161</v>
+        <v>412</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="N53" s="2"/>
+        <v>413</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>414</v>
+      </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>80</v>
@@ -8315,13 +8368,13 @@
         <v>80</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>80</v>
+        <v>195</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>80</v>
+        <v>415</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>80</v>
+        <v>416</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>80</v>
@@ -8339,7 +8392,7 @@
         <v>80</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>163</v>
+        <v>417</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -8348,10 +8401,10 @@
         <v>90</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>164</v>
+        <v>80</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>80</v>
+        <v>102</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>80</v>
@@ -8363,7 +8416,7 @@
         <v>80</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>165</v>
+        <v>144</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>80</v>
@@ -8371,21 +8424,21 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>409</v>
+        <v>418</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>409</v>
+        <v>418</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>137</v>
+        <v>80</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>80</v>
@@ -8394,19 +8447,19 @@
         <v>80</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>138</v>
+        <v>151</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>139</v>
+        <v>419</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>167</v>
+        <v>420</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>141</v>
+        <v>421</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8444,31 +8497,31 @@
         <v>80</v>
       </c>
       <c r="AB54" t="s" s="2">
-        <v>168</v>
+        <v>80</v>
       </c>
       <c r="AC54" t="s" s="2">
-        <v>169</v>
+        <v>80</v>
       </c>
       <c r="AD54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE54" t="s" s="2">
-        <v>170</v>
+        <v>80</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>171</v>
+        <v>422</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>80</v>
+        <v>423</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>143</v>
+        <v>102</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>80</v>
@@ -8480,7 +8533,7 @@
         <v>80</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>80</v>
@@ -8488,10 +8541,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>410</v>
+        <v>424</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>410</v>
+        <v>424</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8508,26 +8561,22 @@
         <v>80</v>
       </c>
       <c r="I55" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>110</v>
+        <v>92</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="O55" t="s" s="2">
-        <v>176</v>
-      </c>
+        <v>168</v>
+      </c>
+      <c r="N55" s="2"/>
+      <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>80</v>
       </c>
@@ -8551,13 +8600,13 @@
         <v>80</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>114</v>
+        <v>80</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>177</v>
+        <v>80</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>178</v>
+        <v>80</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>80</v>
@@ -8575,7 +8624,7 @@
         <v>80</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
@@ -8584,10 +8633,10 @@
         <v>90</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>80</v>
+        <v>170</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>102</v>
+        <v>80</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>80</v>
@@ -8596,10 +8645,10 @@
         <v>80</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>144</v>
+        <v>80</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>180</v>
+        <v>171</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>80</v>
@@ -8607,21 +8656,21 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>411</v>
+        <v>425</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>411</v>
+        <v>425</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>80</v>
+        <v>137</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>80</v>
@@ -8630,23 +8679,21 @@
         <v>80</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>182</v>
+        <v>138</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>183</v>
+        <v>139</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>184</v>
+        <v>174</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>185</v>
-      </c>
-      <c r="O56" t="s" s="2">
-        <v>186</v>
-      </c>
+        <v>141</v>
+      </c>
+      <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>80</v>
       </c>
@@ -8670,43 +8717,43 @@
         <v>80</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>187</v>
+        <v>80</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>188</v>
+        <v>80</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>189</v>
+        <v>80</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AB56" t="s" s="2">
-        <v>80</v>
+        <v>175</v>
       </c>
       <c r="AC56" t="s" s="2">
-        <v>80</v>
+        <v>176</v>
       </c>
       <c r="AD56" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE56" t="s" s="2">
-        <v>80</v>
+        <v>156</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>190</v>
+        <v>177</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>102</v>
+        <v>143</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>80</v>
@@ -8715,10 +8762,10 @@
         <v>80</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>191</v>
+        <v>80</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>180</v>
+        <v>171</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>80</v>
@@ -8726,10 +8773,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>412</v>
+        <v>426</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>412</v>
+        <v>426</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8737,7 +8784,7 @@
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="G57" t="s" s="2">
         <v>90</v>
@@ -8746,25 +8793,25 @@
         <v>80</v>
       </c>
       <c r="I57" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="J57" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>193</v>
+        <v>180</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>194</v>
+        <v>181</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>195</v>
+        <v>182</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>196</v>
+        <v>183</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>80</v>
@@ -8777,7 +8824,7 @@
         <v>80</v>
       </c>
       <c r="T57" t="s" s="2">
-        <v>197</v>
+        <v>80</v>
       </c>
       <c r="U57" t="s" s="2">
         <v>80</v>
@@ -8791,9 +8838,11 @@
       <c r="X57" t="s" s="2">
         <v>114</v>
       </c>
-      <c r="Y57" s="2"/>
+      <c r="Y57" t="s" s="2">
+        <v>184</v>
+      </c>
       <c r="Z57" t="s" s="2">
-        <v>413</v>
+        <v>185</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>80</v>
@@ -8811,7 +8860,7 @@
         <v>80</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
@@ -8832,10 +8881,10 @@
         <v>80</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>199</v>
+        <v>144</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>200</v>
+        <v>187</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>80</v>
@@ -8843,10 +8892,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>414</v>
+        <v>427</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>414</v>
+        <v>427</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8854,7 +8903,7 @@
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="G58" t="s" s="2">
         <v>90</v>
@@ -8869,18 +8918,20 @@
         <v>91</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>202</v>
+        <v>190</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>203</v>
+        <v>191</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>204</v>
+        <v>192</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="O58" s="2"/>
+        <v>193</v>
+      </c>
+      <c r="O58" t="s" s="2">
+        <v>194</v>
+      </c>
       <c r="P58" t="s" s="2">
         <v>80</v>
       </c>
@@ -8892,7 +8943,7 @@
         <v>80</v>
       </c>
       <c r="T58" t="s" s="2">
-        <v>206</v>
+        <v>80</v>
       </c>
       <c r="U58" t="s" s="2">
         <v>80</v>
@@ -8904,13 +8955,13 @@
         <v>80</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>80</v>
+        <v>195</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>80</v>
+        <v>196</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>80</v>
+        <v>197</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>80</v>
@@ -8928,7 +8979,7 @@
         <v>80</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>207</v>
+        <v>198</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
@@ -8937,7 +8988,7 @@
         <v>90</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>208</v>
+        <v>80</v>
       </c>
       <c r="AJ58" t="s" s="2">
         <v>102</v>
@@ -8949,10 +9000,10 @@
         <v>80</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>209</v>
+        <v>199</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>210</v>
+        <v>187</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>80</v>
@@ -8960,10 +9011,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>415</v>
+        <v>428</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>415</v>
+        <v>428</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8971,7 +9022,7 @@
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="G59" t="s" s="2">
         <v>90</v>
@@ -8986,16 +9037,20 @@
         <v>91</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>212</v>
+        <v>104</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>213</v>
+        <v>202</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>214</v>
-      </c>
-      <c r="N59" s="2"/>
-      <c r="O59" s="2"/>
+        <v>203</v>
+      </c>
+      <c r="N59" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="O59" t="s" s="2">
+        <v>205</v>
+      </c>
       <c r="P59" t="s" s="2">
         <v>80</v>
       </c>
@@ -9007,7 +9062,7 @@
         <v>80</v>
       </c>
       <c r="T59" t="s" s="2">
-        <v>80</v>
+        <v>207</v>
       </c>
       <c r="U59" t="s" s="2">
         <v>80</v>
@@ -9019,13 +9074,11 @@
         <v>80</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y59" t="s" s="2">
-        <v>80</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="Y59" s="2"/>
       <c r="Z59" t="s" s="2">
-        <v>80</v>
+        <v>429</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>80</v>
@@ -9043,7 +9096,7 @@
         <v>80</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
@@ -9064,10 +9117,10 @@
         <v>80</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>80</v>
@@ -9075,10 +9128,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>416</v>
+        <v>430</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>416</v>
+        <v>430</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9086,7 +9139,7 @@
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="G60" t="s" s="2">
         <v>90</v>
@@ -9101,16 +9154,16 @@
         <v>91</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -9124,7 +9177,7 @@
         <v>80</v>
       </c>
       <c r="T60" t="s" s="2">
-        <v>80</v>
+        <v>217</v>
       </c>
       <c r="U60" t="s" s="2">
         <v>80</v>
@@ -9160,7 +9213,7 @@
         <v>80</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
@@ -9169,7 +9222,7 @@
         <v>90</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>80</v>
+        <v>219</v>
       </c>
       <c r="AJ60" t="s" s="2">
         <v>102</v>
@@ -9181,10 +9234,10 @@
         <v>80</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>80</v>
@@ -9192,10 +9245,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>417</v>
+        <v>431</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>417</v>
+        <v>431</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9218,17 +9271,15 @@
         <v>91</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>202</v>
+        <v>224</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>418</v>
+        <v>225</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>419</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>420</v>
-      </c>
+        <v>226</v>
+      </c>
+      <c r="N61" s="2"/>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>80</v>
@@ -9277,7 +9328,7 @@
         <v>80</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>421</v>
+        <v>227</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
@@ -9286,7 +9337,7 @@
         <v>90</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>407</v>
+        <v>80</v>
       </c>
       <c r="AJ61" t="s" s="2">
         <v>102</v>
@@ -9298,10 +9349,10 @@
         <v>80</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>80</v>
+        <v>228</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>144</v>
+        <v>229</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>80</v>
@@ -9309,10 +9360,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>422</v>
+        <v>432</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>422</v>
+        <v>432</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9323,7 +9374,7 @@
         <v>78</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>80</v>
@@ -9335,15 +9386,17 @@
         <v>91</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>423</v>
+        <v>232</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>424</v>
+        <v>233</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>425</v>
-      </c>
-      <c r="N62" s="2"/>
+        <v>234</v>
+      </c>
+      <c r="N62" t="s" s="2">
+        <v>235</v>
+      </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>80</v>
@@ -9392,13 +9445,13 @@
         <v>80</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>422</v>
+        <v>236</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>80</v>
@@ -9410,13 +9463,13 @@
         <v>80</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>383</v>
+        <v>80</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>80</v>
+        <v>237</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>426</v>
+        <v>238</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>80</v>
@@ -9424,14 +9477,14 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>427</v>
+        <v>433</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>427</v>
+        <v>433</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>428</v>
+        <v>80</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
@@ -9450,15 +9503,17 @@
         <v>91</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>429</v>
+        <v>213</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="N63" s="2"/>
+        <v>435</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>436</v>
+      </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>80</v>
@@ -9507,7 +9562,7 @@
         <v>80</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>427</v>
+        <v>437</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>78</v>
@@ -9516,44 +9571,44 @@
         <v>90</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>80</v>
+        <v>423</v>
       </c>
       <c r="AJ63" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>432</v>
+        <v>80</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>433</v>
+        <v>80</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>434</v>
+        <v>80</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>435</v>
+        <v>144</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>436</v>
+        <v>80</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>438</v>
+        <v>80</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>80</v>
@@ -9565,13 +9620,13 @@
         <v>91</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>212</v>
+        <v>439</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -9622,13 +9677,13 @@
         <v>80</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>80</v>
@@ -9637,31 +9692,31 @@
         <v>102</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>441</v>
+        <v>80</v>
       </c>
       <c r="AL64" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="AM64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN64" t="s" s="2">
         <v>442</v>
       </c>
-      <c r="AM64" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="AN64" t="s" s="2">
-        <v>444</v>
-      </c>
       <c r="AO64" t="s" s="2">
-        <v>445</v>
+        <v>80</v>
       </c>
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>80</v>
+        <v>444</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
@@ -9680,13 +9735,13 @@
         <v>91</v>
       </c>
       <c r="K65" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="L65" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="M65" t="s" s="2">
         <v>447</v>
-      </c>
-      <c r="L65" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="M65" t="s" s="2">
-        <v>449</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -9713,13 +9768,13 @@
         <v>80</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>289</v>
+        <v>80</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>450</v>
+        <v>80</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>451</v>
+        <v>80</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>80</v>
@@ -9737,7 +9792,7 @@
         <v>80</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>78</v>
@@ -9752,31 +9807,31 @@
         <v>102</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>80</v>
+        <v>448</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>80</v>
+        <v>449</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>80</v>
+        <v>450</v>
       </c>
       <c r="AN65" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="AO65" t="s" s="2">
         <v>452</v>
-      </c>
-      <c r="AO65" t="s" s="2">
-        <v>453</v>
       </c>
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
@@ -9795,13 +9850,13 @@
         <v>91</v>
       </c>
       <c r="K66" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="L66" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="M66" t="s" s="2">
         <v>456</v>
-      </c>
-      <c r="L66" t="s" s="2">
-        <v>457</v>
-      </c>
-      <c r="M66" t="s" s="2">
-        <v>458</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -9852,7 +9907,7 @@
         <v>80</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>78</v>
@@ -9867,35 +9922,35 @@
         <v>102</v>
       </c>
       <c r="AK66" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="AL66" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="AM66" t="s" s="2">
         <v>459</v>
       </c>
-      <c r="AL66" t="s" s="2">
+      <c r="AN66" t="s" s="2">
         <v>460</v>
       </c>
-      <c r="AM66" t="s" s="2">
+      <c r="AO66" t="s" s="2">
         <v>461</v>
-      </c>
-      <c r="AN66" t="s" s="2">
-        <v>462</v>
-      </c>
-      <c r="AO66" t="s" s="2">
-        <v>463</v>
       </c>
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>465</v>
+        <v>80</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="G67" t="s" s="2">
         <v>90</v>
@@ -9910,17 +9965,15 @@
         <v>91</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>468</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>469</v>
-      </c>
+        <v>465</v>
+      </c>
+      <c r="N67" s="2"/>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>80</v>
@@ -9945,13 +9998,13 @@
         <v>80</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>80</v>
+        <v>305</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>80</v>
+        <v>466</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>80</v>
+        <v>467</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>80</v>
@@ -9969,7 +10022,7 @@
         <v>80</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>78</v>
@@ -9984,35 +10037,35 @@
         <v>102</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>470</v>
+        <v>80</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>471</v>
+        <v>80</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>472</v>
+        <v>80</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>473</v>
+        <v>468</v>
       </c>
       <c r="AO67" t="s" s="2">
-        <v>474</v>
+        <v>469</v>
       </c>
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>475</v>
+        <v>470</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>475</v>
+        <v>470</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>476</v>
+        <v>471</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="G68" t="s" s="2">
         <v>90</v>
@@ -10027,17 +10080,15 @@
         <v>91</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>182</v>
+        <v>472</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>478</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>479</v>
-      </c>
+        <v>474</v>
+      </c>
+      <c r="N68" s="2"/>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>80</v>
@@ -10062,13 +10113,13 @@
         <v>80</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>289</v>
+        <v>80</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>480</v>
+        <v>80</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>481</v>
+        <v>80</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>80</v>
@@ -10086,7 +10137,7 @@
         <v>80</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>475</v>
+        <v>470</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>78</v>
@@ -10101,38 +10152,38 @@
         <v>102</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>482</v>
+        <v>475</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>483</v>
+        <v>476</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>484</v>
+        <v>477</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>485</v>
+        <v>478</v>
       </c>
       <c r="AO68" t="s" s="2">
-        <v>80</v>
+        <v>479</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>486</v>
+        <v>480</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>486</v>
+        <v>480</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>487</v>
+        <v>481</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>80</v>
@@ -10144,16 +10195,16 @@
         <v>91</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>488</v>
+        <v>482</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>489</v>
+        <v>483</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>490</v>
+        <v>484</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>491</v>
+        <v>485</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -10203,13 +10254,13 @@
         <v>80</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>486</v>
+        <v>480</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AI69" t="s" s="2">
         <v>80</v>
@@ -10218,38 +10269,38 @@
         <v>102</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>492</v>
+        <v>486</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>493</v>
+        <v>488</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>494</v>
+        <v>489</v>
       </c>
       <c r="AO69" t="s" s="2">
-        <v>80</v>
+        <v>490</v>
       </c>
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>80</v>
+        <v>492</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>80</v>
@@ -10261,15 +10312,17 @@
         <v>91</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>496</v>
+        <v>190</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>498</v>
-      </c>
-      <c r="N70" s="2"/>
+        <v>494</v>
+      </c>
+      <c r="N70" t="s" s="2">
+        <v>495</v>
+      </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>80</v>
@@ -10294,13 +10347,13 @@
         <v>80</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>289</v>
+        <v>305</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>80</v>
@@ -10318,13 +10371,13 @@
         <v>80</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>80</v>
@@ -10333,13 +10386,13 @@
         <v>102</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>80</v>
+        <v>498</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>483</v>
+        <v>499</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>80</v>
+        <v>500</v>
       </c>
       <c r="AN70" t="s" s="2">
         <v>501</v>
@@ -10357,7 +10410,7 @@
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>80</v>
+        <v>503</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
@@ -10376,16 +10429,16 @@
         <v>91</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -10411,13 +10464,13 @@
         <v>80</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>289</v>
+        <v>80</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>507</v>
+        <v>80</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>508</v>
+        <v>80</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>80</v>
@@ -10450,16 +10503,16 @@
         <v>102</v>
       </c>
       <c r="AK71" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="AL71" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="AM71" t="s" s="2">
         <v>509</v>
       </c>
-      <c r="AL71" t="s" s="2">
+      <c r="AN71" t="s" s="2">
         <v>510</v>
-      </c>
-      <c r="AM71" t="s" s="2">
-        <v>511</v>
-      </c>
-      <c r="AN71" t="s" s="2">
-        <v>512</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>80</v>
@@ -10467,10 +10520,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10490,16 +10543,16 @@
         <v>80</v>
       </c>
       <c r="J72" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="K72" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="L72" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="M72" t="s" s="2">
         <v>514</v>
-      </c>
-      <c r="L72" t="s" s="2">
-        <v>515</v>
-      </c>
-      <c r="M72" t="s" s="2">
-        <v>516</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -10526,13 +10579,13 @@
         <v>80</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>80</v>
+        <v>305</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>80</v>
+        <v>515</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>80</v>
+        <v>516</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>80</v>
@@ -10550,7 +10603,7 @@
         <v>80</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>78</v>
@@ -10565,16 +10618,16 @@
         <v>102</v>
       </c>
       <c r="AK72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL72" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="AM72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN72" t="s" s="2">
         <v>517</v>
-      </c>
-      <c r="AL72" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM72" t="s" s="2">
-        <v>518</v>
-      </c>
-      <c r="AN72" t="s" s="2">
-        <v>519</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>80</v>
@@ -10582,14 +10635,14 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>521</v>
+        <v>80</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
@@ -10605,19 +10658,19 @@
         <v>80</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="K73" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="L73" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="M73" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="N73" t="s" s="2">
         <v>522</v>
-      </c>
-      <c r="L73" t="s" s="2">
-        <v>523</v>
-      </c>
-      <c r="M73" t="s" s="2">
-        <v>524</v>
-      </c>
-      <c r="N73" t="s" s="2">
-        <v>525</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -10643,13 +10696,13 @@
         <v>80</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>80</v>
+        <v>305</v>
       </c>
       <c r="Y73" t="s" s="2">
-        <v>80</v>
+        <v>523</v>
       </c>
       <c r="Z73" t="s" s="2">
-        <v>80</v>
+        <v>524</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>80</v>
@@ -10667,7 +10720,7 @@
         <v>80</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>78</v>
@@ -10682,10 +10735,10 @@
         <v>102</v>
       </c>
       <c r="AK73" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="AL73" t="s" s="2">
         <v>526</v>
-      </c>
-      <c r="AL73" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>527</v>
@@ -10722,7 +10775,7 @@
         <v>80</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="K74" t="s" s="2">
         <v>530</v>
@@ -10733,9 +10786,7 @@
       <c r="M74" t="s" s="2">
         <v>532</v>
       </c>
-      <c r="N74" t="s" s="2">
-        <v>533</v>
-      </c>
+      <c r="N74" s="2"/>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
         <v>80</v>
@@ -10799,7 +10850,7 @@
         <v>102</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>80</v>
+        <v>533</v>
       </c>
       <c r="AL74" t="s" s="2">
         <v>80</v>
@@ -10839,23 +10890,21 @@
         <v>80</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>182</v>
+        <v>538</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>540</v>
-      </c>
-      <c r="O75" t="s" s="2">
         <v>541</v>
       </c>
+      <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
         <v>80</v>
       </c>
@@ -10879,13 +10928,13 @@
         <v>80</v>
       </c>
       <c r="X75" t="s" s="2">
-        <v>289</v>
+        <v>80</v>
       </c>
       <c r="Y75" t="s" s="2">
-        <v>542</v>
+        <v>80</v>
       </c>
       <c r="Z75" t="s" s="2">
-        <v>543</v>
+        <v>80</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>80</v>
@@ -10912,44 +10961,44 @@
         <v>79</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>544</v>
+        <v>80</v>
       </c>
       <c r="AJ75" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>80</v>
+        <v>542</v>
       </c>
       <c r="AL75" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>534</v>
+        <v>543</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="AO75" t="s" s="2">
-        <v>546</v>
+        <v>80</v>
       </c>
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>548</v>
+        <v>80</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="H76" t="s" s="2">
         <v>80</v>
@@ -10961,18 +11010,18 @@
         <v>91</v>
       </c>
       <c r="K76" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="L76" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="M76" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="N76" t="s" s="2">
         <v>549</v>
       </c>
-      <c r="L76" t="s" s="2">
-        <v>550</v>
-      </c>
-      <c r="M76" t="s" s="2">
-        <v>539</v>
-      </c>
-      <c r="N76" s="2"/>
-      <c r="O76" t="s" s="2">
-        <v>541</v>
-      </c>
+      <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
         <v>80</v>
       </c>
@@ -11020,16 +11069,16 @@
         <v>80</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AI76" t="s" s="2">
-        <v>544</v>
+        <v>80</v>
       </c>
       <c r="AJ76" t="s" s="2">
         <v>102</v>
@@ -11041,16 +11090,16 @@
         <v>80</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>534</v>
+        <v>550</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>545</v>
+        <v>551</v>
       </c>
       <c r="AO76" t="s" s="2">
-        <v>551</v>
+        <v>80</v>
       </c>
     </row>
-    <row r="77">
+    <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
         <v>552</v>
       </c>
@@ -11059,7 +11108,7 @@
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>80</v>
+        <v>553</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
@@ -11069,25 +11118,29 @@
         <v>79</v>
       </c>
       <c r="H77" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I77" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J77" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="I77" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J77" t="s" s="2">
-        <v>80</v>
-      </c>
       <c r="K77" t="s" s="2">
-        <v>553</v>
+        <v>190</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>49</v>
+        <v>554</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>554</v>
-      </c>
-      <c r="N77" s="2"/>
-      <c r="O77" s="2"/>
+        <v>555</v>
+      </c>
+      <c r="N77" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="O77" t="s" s="2">
+        <v>557</v>
+      </c>
       <c r="P77" t="s" s="2">
         <v>80</v>
       </c>
@@ -11111,13 +11164,13 @@
         <v>80</v>
       </c>
       <c r="X77" t="s" s="2">
-        <v>80</v>
+        <v>305</v>
       </c>
       <c r="Y77" t="s" s="2">
-        <v>80</v>
+        <v>558</v>
       </c>
       <c r="Z77" t="s" s="2">
-        <v>80</v>
+        <v>559</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>80</v>
@@ -11144,44 +11197,44 @@
         <v>79</v>
       </c>
       <c r="AI77" t="s" s="2">
-        <v>80</v>
+        <v>560</v>
       </c>
       <c r="AJ77" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK77" t="s" s="2">
-        <v>555</v>
+        <v>80</v>
       </c>
       <c r="AL77" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>333</v>
+        <v>550</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>556</v>
+        <v>561</v>
       </c>
       <c r="AO77" t="s" s="2">
-        <v>557</v>
+        <v>562</v>
       </c>
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>558</v>
+        <v>563</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>558</v>
+        <v>563</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
-        <v>80</v>
+        <v>564</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>80</v>
@@ -11190,19 +11243,21 @@
         <v>80</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>329</v>
+        <v>565</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>559</v>
+        <v>566</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>560</v>
+        <v>555</v>
       </c>
       <c r="N78" s="2"/>
-      <c r="O78" s="2"/>
+      <c r="O78" t="s" s="2">
+        <v>557</v>
+      </c>
       <c r="P78" t="s" s="2">
         <v>80</v>
       </c>
@@ -11250,16 +11305,16 @@
         <v>80</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>558</v>
+        <v>563</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AI78" t="s" s="2">
-        <v>80</v>
+        <v>560</v>
       </c>
       <c r="AJ78" t="s" s="2">
         <v>102</v>
@@ -11271,21 +11326,21 @@
         <v>80</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>333</v>
+        <v>550</v>
       </c>
       <c r="AN78" t="s" s="2">
         <v>561</v>
       </c>
       <c r="AO78" t="s" s="2">
-        <v>80</v>
+        <v>567</v>
       </c>
     </row>
-    <row r="79" hidden="true">
+    <row r="79">
       <c r="A79" t="s" s="2">
-        <v>562</v>
+        <v>568</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>562</v>
+        <v>568</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11296,10 +11351,10 @@
         <v>78</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="H79" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="I79" t="s" s="2">
         <v>80</v>
@@ -11308,13 +11363,13 @@
         <v>80</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>202</v>
+        <v>569</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>161</v>
+        <v>49</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>162</v>
+        <v>570</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -11365,46 +11420,46 @@
         <v>80</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>163</v>
+        <v>568</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH79" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AI79" t="s" s="2">
-        <v>164</v>
+        <v>80</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>80</v>
+        <v>102</v>
       </c>
       <c r="AK79" t="s" s="2">
-        <v>80</v>
+        <v>571</v>
       </c>
       <c r="AL79" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>80</v>
+        <v>349</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>165</v>
+        <v>572</v>
       </c>
       <c r="AO79" t="s" s="2">
-        <v>80</v>
+        <v>573</v>
       </c>
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>563</v>
+        <v>574</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>563</v>
+        <v>574</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
-        <v>137</v>
+        <v>80</v>
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
@@ -11423,17 +11478,15 @@
         <v>80</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>138</v>
+        <v>345</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>139</v>
+        <v>575</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="N80" t="s" s="2">
-        <v>141</v>
-      </c>
+        <v>576</v>
+      </c>
+      <c r="N80" s="2"/>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
         <v>80</v>
@@ -11482,7 +11535,7 @@
         <v>80</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>171</v>
+        <v>574</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>78</v>
@@ -11494,7 +11547,7 @@
         <v>80</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>143</v>
+        <v>102</v>
       </c>
       <c r="AK80" t="s" s="2">
         <v>80</v>
@@ -11503,10 +11556,10 @@
         <v>80</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>80</v>
+        <v>349</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>165</v>
+        <v>577</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>80</v>
@@ -11514,46 +11567,42 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>564</v>
+        <v>578</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>564</v>
+        <v>578</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
-        <v>337</v>
+        <v>80</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="H81" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I81" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="J81" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>138</v>
+        <v>213</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>338</v>
+        <v>167</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>339</v>
-      </c>
-      <c r="N81" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="O81" t="s" s="2">
-        <v>148</v>
-      </c>
+        <v>168</v>
+      </c>
+      <c r="N81" s="2"/>
+      <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
         <v>80</v>
       </c>
@@ -11601,19 +11650,19 @@
         <v>80</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>340</v>
+        <v>169</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH81" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AI81" t="s" s="2">
-        <v>80</v>
+        <v>170</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>143</v>
+        <v>80</v>
       </c>
       <c r="AK81" t="s" s="2">
         <v>80</v>
@@ -11625,7 +11674,7 @@
         <v>80</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>144</v>
+        <v>171</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>80</v>
@@ -11633,21 +11682,21 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>565</v>
+        <v>579</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>565</v>
+        <v>579</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
-        <v>80</v>
+        <v>137</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="H82" t="s" s="2">
         <v>80</v>
@@ -11656,18 +11705,20 @@
         <v>80</v>
       </c>
       <c r="J82" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>566</v>
+        <v>138</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>559</v>
+        <v>139</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>560</v>
-      </c>
-      <c r="N82" s="2"/>
+        <v>174</v>
+      </c>
+      <c r="N82" t="s" s="2">
+        <v>141</v>
+      </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
         <v>80</v>
@@ -11716,19 +11767,19 @@
         <v>80</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>565</v>
+        <v>177</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AI82" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>102</v>
+        <v>143</v>
       </c>
       <c r="AK82" t="s" s="2">
         <v>80</v>
@@ -11737,10 +11788,10 @@
         <v>80</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>333</v>
+        <v>80</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>561</v>
+        <v>171</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>80</v>
@@ -11748,14 +11799,14 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>567</v>
+        <v>580</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>567</v>
+        <v>580</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
-        <v>80</v>
+        <v>353</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
@@ -11768,24 +11819,26 @@
         <v>80</v>
       </c>
       <c r="I83" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="J83" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>568</v>
+        <v>138</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>569</v>
+        <v>354</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>570</v>
+        <v>355</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>571</v>
-      </c>
-      <c r="O83" s="2"/>
+        <v>141</v>
+      </c>
+      <c r="O83" t="s" s="2">
+        <v>148</v>
+      </c>
       <c r="P83" t="s" s="2">
         <v>80</v>
       </c>
@@ -11833,7 +11886,7 @@
         <v>80</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>567</v>
+        <v>356</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>78</v>
@@ -11845,26 +11898,258 @@
         <v>80</v>
       </c>
       <c r="AJ83" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="AK83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN83" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="AO83" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="84" hidden="true">
+      <c r="A84" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="B84" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="C84" s="2"/>
+      <c r="D84" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E84" s="2"/>
+      <c r="F84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G84" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H84" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I84" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J84" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K84" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="L84" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="M84" t="s" s="2">
+        <v>576</v>
+      </c>
+      <c r="N84" s="2"/>
+      <c r="O84" s="2"/>
+      <c r="P84" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q84" s="2"/>
+      <c r="R84" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S84" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T84" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U84" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V84" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W84" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X84" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y84" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z84" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA84" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB84" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC84" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD84" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE84" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF84" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="AG84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH84" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI84" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ84" t="s" s="2">
         <v>102</v>
       </c>
-      <c r="AK83" t="s" s="2">
-        <v>572</v>
-      </c>
-      <c r="AL83" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM83" t="s" s="2">
+      <c r="AK84" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL84" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM84" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="AN84" t="s" s="2">
+        <v>577</v>
+      </c>
+      <c r="AO84" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="85" hidden="true">
+      <c r="A85" t="s" s="2">
+        <v>583</v>
+      </c>
+      <c r="B85" t="s" s="2">
+        <v>583</v>
+      </c>
+      <c r="C85" s="2"/>
+      <c r="D85" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E85" s="2"/>
+      <c r="F85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G85" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H85" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I85" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J85" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K85" t="s" s="2">
+        <v>584</v>
+      </c>
+      <c r="L85" t="s" s="2">
+        <v>585</v>
+      </c>
+      <c r="M85" t="s" s="2">
+        <v>586</v>
+      </c>
+      <c r="N85" t="s" s="2">
+        <v>587</v>
+      </c>
+      <c r="O85" s="2"/>
+      <c r="P85" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q85" s="2"/>
+      <c r="R85" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S85" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T85" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U85" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V85" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W85" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X85" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y85" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z85" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA85" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB85" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC85" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD85" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE85" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF85" t="s" s="2">
+        <v>583</v>
+      </c>
+      <c r="AG85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH85" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI85" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ85" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK85" t="s" s="2">
+        <v>588</v>
+      </c>
+      <c r="AL85" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM85" t="s" s="2">
         <v>144</v>
       </c>
-      <c r="AN83" t="s" s="2">
-        <v>573</v>
-      </c>
-      <c r="AO83" t="s" s="2">
+      <c r="AN85" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="AO85" t="s" s="2">
         <v>80</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO83">
+  <autoFilter ref="A1:AO85">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -11874,7 +12159,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI82">
+  <conditionalFormatting sqref="A2:AI84">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/currentbuild/StructureDefinition-parek-service-request.xlsx
+++ b/currentbuild/StructureDefinition-parek-service-request.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-10T11:25:48+00:00</t>
+    <t>2026-04-10T11:43:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/StructureDefinition-parek-service-request.xlsx
+++ b/currentbuild/StructureDefinition-parek-service-request.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-10T11:43:13+00:00</t>
+    <t>2026-04-10T11:51:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/StructureDefinition-parek-service-request.xlsx
+++ b/currentbuild/StructureDefinition-parek-service-request.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-10T11:51:44+00:00</t>
+    <t>2026-04-10T12:03:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/StructureDefinition-parek-service-request.xlsx
+++ b/currentbuild/StructureDefinition-parek-service-request.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-10T12:03:27+00:00</t>
+    <t>2026-04-10T12:17:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/StructureDefinition-parek-service-request.xlsx
+++ b/currentbuild/StructureDefinition-parek-service-request.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-10T12:17:42+00:00</t>
+    <t>2026-04-10T12:43:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/StructureDefinition-parek-service-request.xlsx
+++ b/currentbuild/StructureDefinition-parek-service-request.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-10T12:43:41+00:00</t>
+    <t>2026-04-10T12:51:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/StructureDefinition-parek-service-request.xlsx
+++ b/currentbuild/StructureDefinition-parek-service-request.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-10T12:51:31+00:00</t>
+    <t>2026-04-10T13:11:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/StructureDefinition-parek-service-request.xlsx
+++ b/currentbuild/StructureDefinition-parek-service-request.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.4</t>
+    <t>0.1.5</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-10T13:11:24+00:00</t>
+    <t>2026-04-13T12:24:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/StructureDefinition-parek-service-request.xlsx
+++ b/currentbuild/StructureDefinition-parek-service-request.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-13T12:24:04+00:00</t>
+    <t>2026-04-13T13:08:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/StructureDefinition-parek-service-request.xlsx
+++ b/currentbuild/StructureDefinition-parek-service-request.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3171" uniqueCount="590">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3171" uniqueCount="591">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.5</t>
+    <t>0.1.6</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-13T13:08:41+00:00</t>
+    <t>2026-04-15T12:03:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1356,7 +1356,7 @@
     <t>ServiceRequest.subject.identifier.system</t>
   </si>
   <si>
-    <t>http://hl7.no/fhir/ig/ParekIG/ValueSet/public-id-type-vs</t>
+    <t>http://hl7.no/fhir/ig/ParekIG/ValueSet/person-public-id-type-vs</t>
   </si>
   <si>
     <t>ServiceRequest.subject.identifier.value</t>
@@ -1534,6 +1534,10 @@
   </si>
   <si>
     <t>This not the dispatcher, but rather who is the authorizer.  This element is not intended to handle delegation which would generally be managed through the Provenance resource.</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+local-reference-only:Referansen må være lokal (starte med #) og peke til en inneholdt ressurs. {reference.startsWith('#')}</t>
   </si>
   <si>
     <t>Request.requester</t>
@@ -5864,7 +5868,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
         <v>329</v>
       </c>
@@ -5877,13 +5881,13 @@
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="G32" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>80</v>
@@ -10266,34 +10270,34 @@
         <v>80</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>102</v>
+        <v>486</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="AO69" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
@@ -10315,13 +10319,13 @@
         <v>190</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -10350,10 +10354,10 @@
         <v>305</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>80</v>
@@ -10371,7 +10375,7 @@
         <v>80</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>78</v>
@@ -10386,16 +10390,16 @@
         <v>102</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>80</v>
@@ -10403,14 +10407,14 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
@@ -10429,16 +10433,16 @@
         <v>91</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -10488,7 +10492,7 @@
         <v>80</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>78</v>
@@ -10503,16 +10507,16 @@
         <v>102</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>80</v>
@@ -10520,10 +10524,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10546,13 +10550,13 @@
         <v>91</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -10582,10 +10586,10 @@
         <v>305</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>80</v>
@@ -10603,7 +10607,7 @@
         <v>80</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>78</v>
@@ -10621,13 +10625,13 @@
         <v>80</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>80</v>
@@ -10635,10 +10639,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10661,16 +10665,16 @@
         <v>91</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -10699,10 +10703,10 @@
         <v>305</v>
       </c>
       <c r="Y73" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="Z73" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>80</v>
@@ -10720,7 +10724,7 @@
         <v>80</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>78</v>
@@ -10735,16 +10739,16 @@
         <v>102</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>80</v>
@@ -10752,10 +10756,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10778,13 +10782,13 @@
         <v>80</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -10835,7 +10839,7 @@
         <v>80</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>78</v>
@@ -10850,16 +10854,16 @@
         <v>102</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="AL74" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>80</v>
@@ -10867,14 +10871,14 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
@@ -10893,16 +10897,16 @@
         <v>80</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -10952,7 +10956,7 @@
         <v>80</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>78</v>
@@ -10967,16 +10971,16 @@
         <v>102</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="AL75" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>80</v>
@@ -10984,10 +10988,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11010,16 +11014,16 @@
         <v>91</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -11069,7 +11073,7 @@
         <v>80</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>78</v>
@@ -11090,10 +11094,10 @@
         <v>80</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>80</v>
@@ -11101,14 +11105,14 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
@@ -11130,16 +11134,16 @@
         <v>190</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="O77" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>80</v>
@@ -11167,10 +11171,10 @@
         <v>305</v>
       </c>
       <c r="Y77" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="Z77" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>80</v>
@@ -11188,7 +11192,7 @@
         <v>80</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>78</v>
@@ -11197,7 +11201,7 @@
         <v>79</v>
       </c>
       <c r="AI77" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="AJ77" t="s" s="2">
         <v>102</v>
@@ -11209,25 +11213,25 @@
         <v>80</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="AO77" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
@@ -11246,17 +11250,17 @@
         <v>91</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>80</v>
@@ -11305,7 +11309,7 @@
         <v>80</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>78</v>
@@ -11314,7 +11318,7 @@
         <v>90</v>
       </c>
       <c r="AI78" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="AJ78" t="s" s="2">
         <v>102</v>
@@ -11326,21 +11330,21 @@
         <v>80</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="AO78" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11363,13 +11367,13 @@
         <v>80</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="L79" t="s" s="2">
         <v>49</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -11420,7 +11424,7 @@
         <v>80</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>78</v>
@@ -11435,7 +11439,7 @@
         <v>102</v>
       </c>
       <c r="AK79" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="AL79" t="s" s="2">
         <v>80</v>
@@ -11444,18 +11448,18 @@
         <v>349</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="AO79" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11481,10 +11485,10 @@
         <v>345</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -11535,7 +11539,7 @@
         <v>80</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>78</v>
@@ -11559,7 +11563,7 @@
         <v>349</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>80</v>
@@ -11567,10 +11571,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11682,10 +11686,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11799,10 +11803,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11918,10 +11922,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -11944,13 +11948,13 @@
         <v>91</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
@@ -12001,7 +12005,7 @@
         <v>80</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>78</v>
@@ -12025,7 +12029,7 @@
         <v>349</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>80</v>
@@ -12033,10 +12037,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12059,16 +12063,16 @@
         <v>80</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -12118,7 +12122,7 @@
         <v>80</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>78</v>
@@ -12133,7 +12137,7 @@
         <v>102</v>
       </c>
       <c r="AK85" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="AL85" t="s" s="2">
         <v>80</v>
@@ -12142,7 +12146,7 @@
         <v>144</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>80</v>

--- a/currentbuild/StructureDefinition-parek-service-request.xlsx
+++ b/currentbuild/StructureDefinition-parek-service-request.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$85</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$89</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3171" uniqueCount="591">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3319" uniqueCount="609">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.6</t>
+    <t>0.1.7</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-15T12:03:39+00:00</t>
+    <t>2026-04-16T08:13:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1459,6 +1459,65 @@
     <t>Procedure.procedureSchedule</t>
   </si>
   <si>
+    <t>ServiceRequest.occurrence[x].id</t>
+  </si>
+  <si>
+    <t>ServiceRequest.occurrence[x].extension</t>
+  </si>
+  <si>
+    <t>ServiceRequest.occurrence[x].start</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dateTime
+</t>
+  </si>
+  <si>
+    <t>Starting time with inclusive boundary</t>
+  </si>
+  <si>
+    <t>The start of the period. The boundary is inclusive.</t>
+  </si>
+  <si>
+    <t>If the low element is missing, the meaning is that the low boundary is not known.</t>
+  </si>
+  <si>
+    <t>Period.start</t>
+  </si>
+  <si>
+    <t xml:space="preserve">per-1
+</t>
+  </si>
+  <si>
+    <t>DR.1</t>
+  </si>
+  <si>
+    <t>./low</t>
+  </si>
+  <si>
+    <t>ServiceRequest.occurrence[x].end</t>
+  </si>
+  <si>
+    <t>End time with inclusive boundary, if not ongoing</t>
+  </si>
+  <si>
+    <t>The end of the period. If the end of the period is missing, it means no end was known or planned at the time the instance was created. The start may be in the past, and the end date in the future, which means that period is expected/planned to end at that time.</t>
+  </si>
+  <si>
+    <t>The end value includes any matching date/time. i.e. 2012-02-03T10:00:00 is in a period that has an end value of 2012-02-03.</t>
+  </si>
+  <si>
+    <t>If the end of the period is missing, it means that the period is ongoing</t>
+  </si>
+  <si>
+    <t>Period.end</t>
+  </si>
+  <si>
+    <t>DR.2</t>
+  </si>
+  <si>
+    <t>./high</t>
+  </si>
+  <si>
     <t>ServiceRequest.asNeeded[x]</t>
   </si>
   <si>
@@ -1488,10 +1547,6 @@
   </si>
   <si>
     <t xml:space="preserve">orderedOn
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dateTime
 </t>
   </si>
   <si>
@@ -2182,7 +2237,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO85"/>
+  <dimension ref="A1:AO89"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="47.2109375" customWidth="true" bestFit="true"/>
@@ -9966,16 +10021,16 @@
         <v>80</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>463</v>
+        <v>92</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>464</v>
+        <v>167</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>465</v>
+        <v>168</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -10002,13 +10057,13 @@
         <v>80</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>305</v>
+        <v>80</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>466</v>
+        <v>80</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>467</v>
+        <v>80</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>80</v>
@@ -10026,7 +10081,7 @@
         <v>80</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>462</v>
+        <v>169</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>78</v>
@@ -10035,10 +10090,10 @@
         <v>90</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>80</v>
+        <v>170</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>102</v>
+        <v>80</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>80</v>
@@ -10050,29 +10105,29 @@
         <v>80</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>468</v>
+        <v>171</v>
       </c>
       <c r="AO67" t="s" s="2">
-        <v>469</v>
+        <v>80</v>
       </c>
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>470</v>
+        <v>463</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>470</v>
+        <v>463</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>471</v>
+        <v>137</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>80</v>
@@ -10081,18 +10136,20 @@
         <v>80</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>472</v>
+        <v>138</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>473</v>
+        <v>139</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>474</v>
-      </c>
-      <c r="N68" s="2"/>
+        <v>174</v>
+      </c>
+      <c r="N68" t="s" s="2">
+        <v>141</v>
+      </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>80</v>
@@ -10129,62 +10186,62 @@
         <v>80</v>
       </c>
       <c r="AB68" t="s" s="2">
-        <v>80</v>
+        <v>175</v>
       </c>
       <c r="AC68" t="s" s="2">
-        <v>80</v>
+        <v>176</v>
       </c>
       <c r="AD68" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE68" t="s" s="2">
-        <v>80</v>
+        <v>156</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>470</v>
+        <v>177</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>102</v>
+        <v>143</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>475</v>
+        <v>80</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>476</v>
+        <v>80</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>477</v>
+        <v>80</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>478</v>
+        <v>171</v>
       </c>
       <c r="AO68" t="s" s="2">
-        <v>479</v>
+        <v>80</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>480</v>
+        <v>464</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>480</v>
+        <v>464</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>481</v>
+        <v>80</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="G69" t="s" s="2">
         <v>90</v>
@@ -10199,16 +10256,16 @@
         <v>91</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>482</v>
+        <v>465</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>483</v>
+        <v>466</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>484</v>
+        <v>467</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>485</v>
+        <v>468</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -10258,7 +10315,7 @@
         <v>80</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>480</v>
+        <v>469</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>78</v>
@@ -10267,41 +10324,41 @@
         <v>90</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>80</v>
+        <v>470</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>486</v>
+        <v>102</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>487</v>
+        <v>80</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>488</v>
+        <v>80</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>489</v>
+        <v>471</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>490</v>
+        <v>472</v>
       </c>
       <c r="AO69" t="s" s="2">
-        <v>491</v>
+        <v>80</v>
       </c>
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>492</v>
+        <v>473</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>492</v>
+        <v>473</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>493</v>
+        <v>80</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="G70" t="s" s="2">
         <v>90</v>
@@ -10316,22 +10373,24 @@
         <v>91</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>190</v>
+        <v>465</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>494</v>
+        <v>474</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>495</v>
+        <v>475</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>496</v>
+        <v>476</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>80</v>
       </c>
-      <c r="Q70" s="2"/>
+      <c r="Q70" t="s" s="2">
+        <v>477</v>
+      </c>
       <c r="R70" t="s" s="2">
         <v>80</v>
       </c>
@@ -10351,13 +10410,13 @@
         <v>80</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>305</v>
+        <v>80</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>497</v>
+        <v>80</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>498</v>
+        <v>80</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>80</v>
@@ -10375,7 +10434,7 @@
         <v>80</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>492</v>
+        <v>478</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>78</v>
@@ -10384,22 +10443,22 @@
         <v>90</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>80</v>
+        <v>470</v>
       </c>
       <c r="AJ70" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>499</v>
+        <v>80</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>500</v>
+        <v>80</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>501</v>
+        <v>479</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>502</v>
+        <v>480</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>80</v>
@@ -10407,21 +10466,21 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>503</v>
+        <v>481</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>503</v>
+        <v>481</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>504</v>
+        <v>80</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>80</v>
@@ -10433,17 +10492,15 @@
         <v>91</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>505</v>
+        <v>482</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>506</v>
+        <v>483</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>507</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>508</v>
-      </c>
+        <v>484</v>
+      </c>
+      <c r="N71" s="2"/>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
         <v>80</v>
@@ -10468,13 +10525,13 @@
         <v>80</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>80</v>
+        <v>305</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>80</v>
+        <v>485</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>80</v>
+        <v>486</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>80</v>
@@ -10492,13 +10549,13 @@
         <v>80</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>503</v>
+        <v>481</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>80</v>
@@ -10507,38 +10564,38 @@
         <v>102</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>509</v>
+        <v>80</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>500</v>
+        <v>80</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>510</v>
+        <v>80</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>511</v>
+        <v>487</v>
       </c>
       <c r="AO71" t="s" s="2">
-        <v>80</v>
+        <v>488</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>512</v>
+        <v>489</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>512</v>
+        <v>489</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>80</v>
+        <v>490</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>80</v>
@@ -10550,13 +10607,13 @@
         <v>91</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>513</v>
+        <v>465</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>514</v>
+        <v>491</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>515</v>
+        <v>492</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -10583,13 +10640,13 @@
         <v>80</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>305</v>
+        <v>80</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>516</v>
+        <v>80</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>517</v>
+        <v>80</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>80</v>
@@ -10607,13 +10664,13 @@
         <v>80</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>512</v>
+        <v>489</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>80</v>
@@ -10622,38 +10679,38 @@
         <v>102</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>80</v>
+        <v>493</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>500</v>
+        <v>494</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>80</v>
+        <v>495</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>518</v>
+        <v>496</v>
       </c>
       <c r="AO72" t="s" s="2">
-        <v>80</v>
+        <v>497</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>519</v>
+        <v>498</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>519</v>
+        <v>498</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>80</v>
+        <v>499</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>80</v>
@@ -10665,16 +10722,16 @@
         <v>91</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>520</v>
+        <v>500</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>521</v>
+        <v>501</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>522</v>
+        <v>502</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>523</v>
+        <v>503</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -10700,13 +10757,13 @@
         <v>80</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>305</v>
+        <v>80</v>
       </c>
       <c r="Y73" t="s" s="2">
-        <v>524</v>
+        <v>80</v>
       </c>
       <c r="Z73" t="s" s="2">
-        <v>525</v>
+        <v>80</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>80</v>
@@ -10724,53 +10781,53 @@
         <v>80</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>519</v>
+        <v>498</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>102</v>
+        <v>504</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>526</v>
+        <v>505</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>527</v>
+        <v>506</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>528</v>
+        <v>507</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>529</v>
+        <v>508</v>
       </c>
       <c r="AO73" t="s" s="2">
-        <v>80</v>
+        <v>509</v>
       </c>
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>530</v>
+        <v>510</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>530</v>
+        <v>510</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>80</v>
+        <v>511</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>80</v>
@@ -10779,18 +10836,20 @@
         <v>80</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>531</v>
+        <v>190</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>532</v>
+        <v>512</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>533</v>
-      </c>
-      <c r="N74" s="2"/>
+        <v>513</v>
+      </c>
+      <c r="N74" t="s" s="2">
+        <v>514</v>
+      </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
         <v>80</v>
@@ -10815,13 +10874,13 @@
         <v>80</v>
       </c>
       <c r="X74" t="s" s="2">
-        <v>80</v>
+        <v>305</v>
       </c>
       <c r="Y74" t="s" s="2">
-        <v>80</v>
+        <v>515</v>
       </c>
       <c r="Z74" t="s" s="2">
-        <v>80</v>
+        <v>516</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>80</v>
@@ -10839,13 +10898,13 @@
         <v>80</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>530</v>
+        <v>510</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AI74" t="s" s="2">
         <v>80</v>
@@ -10854,16 +10913,16 @@
         <v>102</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>534</v>
+        <v>517</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>80</v>
+        <v>518</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>535</v>
+        <v>519</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>536</v>
+        <v>520</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>80</v>
@@ -10871,14 +10930,14 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>537</v>
+        <v>521</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>537</v>
+        <v>521</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>538</v>
+        <v>522</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
@@ -10894,19 +10953,19 @@
         <v>80</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>539</v>
+        <v>523</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>540</v>
+        <v>524</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>541</v>
+        <v>525</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>542</v>
+        <v>526</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -10956,7 +11015,7 @@
         <v>80</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>537</v>
+        <v>521</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>78</v>
@@ -10971,16 +11030,16 @@
         <v>102</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>543</v>
+        <v>527</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>80</v>
+        <v>518</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>544</v>
+        <v>528</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>545</v>
+        <v>529</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>80</v>
@@ -10988,10 +11047,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>546</v>
+        <v>530</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>546</v>
+        <v>530</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11014,17 +11073,15 @@
         <v>91</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>547</v>
+        <v>531</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>548</v>
+        <v>532</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>549</v>
-      </c>
-      <c r="N76" t="s" s="2">
-        <v>550</v>
-      </c>
+        <v>533</v>
+      </c>
+      <c r="N76" s="2"/>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
         <v>80</v>
@@ -11049,13 +11106,13 @@
         <v>80</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>80</v>
+        <v>305</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>80</v>
+        <v>534</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>80</v>
+        <v>535</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>80</v>
@@ -11073,7 +11130,7 @@
         <v>80</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>546</v>
+        <v>530</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>78</v>
@@ -11091,13 +11148,13 @@
         <v>80</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>80</v>
+        <v>518</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>551</v>
+        <v>80</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>552</v>
+        <v>536</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>80</v>
@@ -11105,14 +11162,14 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>553</v>
+        <v>537</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>553</v>
+        <v>537</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>554</v>
+        <v>80</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
@@ -11131,20 +11188,18 @@
         <v>91</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>190</v>
+        <v>538</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>555</v>
+        <v>539</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>556</v>
+        <v>540</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>557</v>
-      </c>
-      <c r="O77" t="s" s="2">
-        <v>558</v>
-      </c>
+        <v>541</v>
+      </c>
+      <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
         <v>80</v>
       </c>
@@ -11171,10 +11226,10 @@
         <v>305</v>
       </c>
       <c r="Y77" t="s" s="2">
-        <v>559</v>
+        <v>542</v>
       </c>
       <c r="Z77" t="s" s="2">
-        <v>560</v>
+        <v>543</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>80</v>
@@ -11192,7 +11247,7 @@
         <v>80</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>553</v>
+        <v>537</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>78</v>
@@ -11201,44 +11256,44 @@
         <v>79</v>
       </c>
       <c r="AI77" t="s" s="2">
-        <v>561</v>
+        <v>80</v>
       </c>
       <c r="AJ77" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK77" t="s" s="2">
-        <v>80</v>
+        <v>544</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>80</v>
+        <v>545</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>551</v>
+        <v>546</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>562</v>
+        <v>547</v>
       </c>
       <c r="AO77" t="s" s="2">
-        <v>563</v>
+        <v>80</v>
       </c>
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>564</v>
+        <v>548</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>564</v>
+        <v>548</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
-        <v>565</v>
+        <v>80</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>80</v>
@@ -11247,21 +11302,19 @@
         <v>80</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>566</v>
+        <v>549</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>567</v>
+        <v>550</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>556</v>
+        <v>551</v>
       </c>
       <c r="N78" s="2"/>
-      <c r="O78" t="s" s="2">
-        <v>558</v>
-      </c>
+      <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
         <v>80</v>
       </c>
@@ -11309,46 +11362,46 @@
         <v>80</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>564</v>
+        <v>548</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AI78" t="s" s="2">
-        <v>561</v>
+        <v>80</v>
       </c>
       <c r="AJ78" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK78" t="s" s="2">
-        <v>80</v>
+        <v>552</v>
       </c>
       <c r="AL78" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>562</v>
+        <v>554</v>
       </c>
       <c r="AO78" t="s" s="2">
-        <v>568</v>
+        <v>80</v>
       </c>
     </row>
-    <row r="79">
+    <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>569</v>
+        <v>555</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>569</v>
+        <v>555</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
-        <v>80</v>
+        <v>556</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
@@ -11358,7 +11411,7 @@
         <v>79</v>
       </c>
       <c r="H79" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="I79" t="s" s="2">
         <v>80</v>
@@ -11367,15 +11420,17 @@
         <v>80</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>570</v>
+        <v>557</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>49</v>
+        <v>558</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>571</v>
-      </c>
-      <c r="N79" s="2"/>
+        <v>559</v>
+      </c>
+      <c r="N79" t="s" s="2">
+        <v>560</v>
+      </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
         <v>80</v>
@@ -11424,7 +11479,7 @@
         <v>80</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>569</v>
+        <v>555</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>78</v>
@@ -11439,27 +11494,27 @@
         <v>102</v>
       </c>
       <c r="AK79" t="s" s="2">
-        <v>572</v>
+        <v>561</v>
       </c>
       <c r="AL79" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>349</v>
+        <v>562</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>573</v>
+        <v>563</v>
       </c>
       <c r="AO79" t="s" s="2">
-        <v>574</v>
+        <v>80</v>
       </c>
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>575</v>
+        <v>564</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>575</v>
+        <v>564</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11479,18 +11534,20 @@
         <v>80</v>
       </c>
       <c r="J80" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>345</v>
+        <v>565</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>576</v>
+        <v>566</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>577</v>
-      </c>
-      <c r="N80" s="2"/>
+        <v>567</v>
+      </c>
+      <c r="N80" t="s" s="2">
+        <v>568</v>
+      </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
         <v>80</v>
@@ -11539,7 +11596,7 @@
         <v>80</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>575</v>
+        <v>564</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>78</v>
@@ -11560,10 +11617,10 @@
         <v>80</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>349</v>
+        <v>569</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>578</v>
+        <v>570</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>80</v>
@@ -11571,21 +11628,21 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>579</v>
+        <v>571</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>579</v>
+        <v>571</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
-        <v>80</v>
+        <v>572</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="H81" t="s" s="2">
         <v>80</v>
@@ -11594,19 +11651,23 @@
         <v>80</v>
       </c>
       <c r="J81" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>213</v>
+        <v>190</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>167</v>
+        <v>573</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="N81" s="2"/>
-      <c r="O81" s="2"/>
+        <v>574</v>
+      </c>
+      <c r="N81" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="O81" t="s" s="2">
+        <v>576</v>
+      </c>
       <c r="P81" t="s" s="2">
         <v>80</v>
       </c>
@@ -11630,13 +11691,13 @@
         <v>80</v>
       </c>
       <c r="X81" t="s" s="2">
-        <v>80</v>
+        <v>305</v>
       </c>
       <c r="Y81" t="s" s="2">
-        <v>80</v>
+        <v>577</v>
       </c>
       <c r="Z81" t="s" s="2">
-        <v>80</v>
+        <v>578</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>80</v>
@@ -11654,19 +11715,19 @@
         <v>80</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>169</v>
+        <v>571</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH81" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AI81" t="s" s="2">
-        <v>170</v>
+        <v>579</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>80</v>
+        <v>102</v>
       </c>
       <c r="AK81" t="s" s="2">
         <v>80</v>
@@ -11675,32 +11736,32 @@
         <v>80</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>80</v>
+        <v>569</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>171</v>
+        <v>580</v>
       </c>
       <c r="AO81" t="s" s="2">
-        <v>80</v>
+        <v>581</v>
       </c>
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
-        <v>137</v>
+        <v>583</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="H82" t="s" s="2">
         <v>80</v>
@@ -11709,21 +11770,21 @@
         <v>80</v>
       </c>
       <c r="J82" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>138</v>
+        <v>584</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>139</v>
+        <v>585</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="N82" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="O82" s="2"/>
+        <v>574</v>
+      </c>
+      <c r="N82" s="2"/>
+      <c r="O82" t="s" s="2">
+        <v>576</v>
+      </c>
       <c r="P82" t="s" s="2">
         <v>80</v>
       </c>
@@ -11771,19 +11832,19 @@
         <v>80</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>177</v>
+        <v>582</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AI82" t="s" s="2">
-        <v>80</v>
+        <v>579</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>143</v>
+        <v>102</v>
       </c>
       <c r="AK82" t="s" s="2">
         <v>80</v>
@@ -11792,25 +11853,25 @@
         <v>80</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>80</v>
+        <v>569</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>171</v>
+        <v>580</v>
       </c>
       <c r="AO82" t="s" s="2">
-        <v>80</v>
+        <v>586</v>
       </c>
     </row>
-    <row r="83" hidden="true">
+    <row r="83">
       <c r="A83" t="s" s="2">
-        <v>581</v>
+        <v>587</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>581</v>
+        <v>587</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
-        <v>353</v>
+        <v>80</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
@@ -11820,29 +11881,25 @@
         <v>79</v>
       </c>
       <c r="H83" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="I83" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="J83" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>138</v>
+        <v>588</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>354</v>
+        <v>49</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>355</v>
-      </c>
-      <c r="N83" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="O83" t="s" s="2">
-        <v>148</v>
-      </c>
+        <v>589</v>
+      </c>
+      <c r="N83" s="2"/>
+      <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
         <v>80</v>
       </c>
@@ -11890,7 +11947,7 @@
         <v>80</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>356</v>
+        <v>587</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>78</v>
@@ -11902,30 +11959,30 @@
         <v>80</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>143</v>
+        <v>102</v>
       </c>
       <c r="AK83" t="s" s="2">
-        <v>80</v>
+        <v>590</v>
       </c>
       <c r="AL83" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>80</v>
+        <v>349</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>144</v>
+        <v>591</v>
       </c>
       <c r="AO83" t="s" s="2">
-        <v>80</v>
+        <v>592</v>
       </c>
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>582</v>
+        <v>593</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>582</v>
+        <v>593</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -11936,7 +11993,7 @@
         <v>78</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="H84" t="s" s="2">
         <v>80</v>
@@ -11945,16 +12002,16 @@
         <v>80</v>
       </c>
       <c r="J84" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>583</v>
+        <v>345</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>576</v>
+        <v>594</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>577</v>
+        <v>595</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
@@ -12005,13 +12062,13 @@
         <v>80</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>582</v>
+        <v>593</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH84" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AI84" t="s" s="2">
         <v>80</v>
@@ -12029,7 +12086,7 @@
         <v>349</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>578</v>
+        <v>596</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>80</v>
@@ -12037,10 +12094,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>584</v>
+        <v>597</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>584</v>
+        <v>597</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12051,7 +12108,7 @@
         <v>78</v>
       </c>
       <c r="G85" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="H85" t="s" s="2">
         <v>80</v>
@@ -12063,17 +12120,15 @@
         <v>80</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>585</v>
+        <v>213</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>586</v>
+        <v>167</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>587</v>
-      </c>
-      <c r="N85" t="s" s="2">
-        <v>588</v>
-      </c>
+        <v>168</v>
+      </c>
+      <c r="N85" s="2"/>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
         <v>80</v>
@@ -12122,38 +12177,506 @@
         <v>80</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>584</v>
+        <v>169</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH85" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI85" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="AJ85" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AK85" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL85" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM85" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN85" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="AO85" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="86" hidden="true">
+      <c r="A86" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="B86" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="C86" s="2"/>
+      <c r="D86" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="E86" s="2"/>
+      <c r="F86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G86" t="s" s="2">
         <v>79</v>
       </c>
-      <c r="AI85" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ85" t="s" s="2">
+      <c r="H86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K86" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="L86" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="M86" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="N86" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="O86" s="2"/>
+      <c r="P86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q86" s="2"/>
+      <c r="R86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF86" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="AG86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH86" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ86" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="AK86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN86" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="AO86" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="87" hidden="true">
+      <c r="A87" t="s" s="2">
+        <v>599</v>
+      </c>
+      <c r="B87" t="s" s="2">
+        <v>599</v>
+      </c>
+      <c r="C87" s="2"/>
+      <c r="D87" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="E87" s="2"/>
+      <c r="F87" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G87" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I87" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="J87" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K87" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="L87" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="M87" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="N87" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="O87" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="P87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q87" s="2"/>
+      <c r="R87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF87" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="AG87" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH87" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ87" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="AK87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN87" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="AO87" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="88" hidden="true">
+      <c r="A88" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="B88" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="C88" s="2"/>
+      <c r="D88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E88" s="2"/>
+      <c r="F88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G88" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J88" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K88" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="L88" t="s" s="2">
+        <v>594</v>
+      </c>
+      <c r="M88" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="N88" s="2"/>
+      <c r="O88" s="2"/>
+      <c r="P88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q88" s="2"/>
+      <c r="R88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF88" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="AG88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH88" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ88" t="s" s="2">
         <v>102</v>
       </c>
-      <c r="AK85" t="s" s="2">
-        <v>589</v>
-      </c>
-      <c r="AL85" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM85" t="s" s="2">
+      <c r="AK88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM88" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="AN88" t="s" s="2">
+        <v>596</v>
+      </c>
+      <c r="AO88" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="89" hidden="true">
+      <c r="A89" t="s" s="2">
+        <v>602</v>
+      </c>
+      <c r="B89" t="s" s="2">
+        <v>602</v>
+      </c>
+      <c r="C89" s="2"/>
+      <c r="D89" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E89" s="2"/>
+      <c r="F89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G89" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H89" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I89" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J89" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K89" t="s" s="2">
+        <v>603</v>
+      </c>
+      <c r="L89" t="s" s="2">
+        <v>604</v>
+      </c>
+      <c r="M89" t="s" s="2">
+        <v>605</v>
+      </c>
+      <c r="N89" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="O89" s="2"/>
+      <c r="P89" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q89" s="2"/>
+      <c r="R89" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S89" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T89" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U89" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V89" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W89" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X89" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y89" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z89" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA89" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB89" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC89" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD89" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE89" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF89" t="s" s="2">
+        <v>602</v>
+      </c>
+      <c r="AG89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH89" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI89" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ89" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK89" t="s" s="2">
+        <v>607</v>
+      </c>
+      <c r="AL89" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM89" t="s" s="2">
         <v>144</v>
       </c>
-      <c r="AN85" t="s" s="2">
-        <v>590</v>
-      </c>
-      <c r="AO85" t="s" s="2">
+      <c r="AN89" t="s" s="2">
+        <v>608</v>
+      </c>
+      <c r="AO89" t="s" s="2">
         <v>80</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO85">
+  <autoFilter ref="A1:AO89">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -12163,7 +12686,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI84">
+  <conditionalFormatting sqref="A2:AI88">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>
